--- a/precios_catalogo.xlsx
+++ b/precios_catalogo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G265"/>
+  <dimension ref="A1:G442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9073,6 +9073,5359 @@
       </c>
       <c r="G265" t="inlineStr"/>
     </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>MQ-ENR-01</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Mosquitera Enrollable Ventana 42 - Grupo 1 (Blanco)</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>48</v>
+      </c>
+      <c r="D266" t="n">
+        <v>36</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>MQ-ENR-02</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Mosquitera Enrollable Ventana 42 - Grupo 2 (Plata/Bronce/RAL)</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>54</v>
+      </c>
+      <c r="D267" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>MQ-ENR-03</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Mosquitera Enrollable Ventana 42 - Grupo 3 (Madera)</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>62</v>
+      </c>
+      <c r="D268" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>MQ-ENR-PTA1</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Mosquitera Enrollable Puerta Lateral Única - Grupo 1</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>125</v>
+      </c>
+      <c r="D269" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>MQ-ENR-PTA2</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Mosquitera Enrollable Puerta Lateral Doble - Grupo 1</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>230</v>
+      </c>
+      <c r="D270" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>MQ-PLI-22-1</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Mosquitera Plisada 22 Puerta Única - Grupo 1</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>135</v>
+      </c>
+      <c r="D271" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>MQ-PLI-22-2</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Mosquitera Plisada 22 Puerta Doble - Grupo 1</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>245</v>
+      </c>
+      <c r="D272" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>MQ-PLI-22-REV</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Mosquitera Plisada 22 Reversible - Grupo 1</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>155</v>
+      </c>
+      <c r="D273" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>MQ-PLI-22-VEN</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Mosquitera Plisada 22 Ventana - Grupo 1</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>85</v>
+      </c>
+      <c r="D274" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>MQ-PLI-40-1</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Mosquitera Plisada 40 Puerta Única - Grupo 1</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>326</v>
+      </c>
+      <c r="D275" t="n">
+        <v>244.5</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>MQ-PLI-40-2</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Mosquitera Plisada 40 Puerta Doble - Grupo 1</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>653</v>
+      </c>
+      <c r="D276" t="n">
+        <v>489.75</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>MQ-ABA-1</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Mosquitera Abatible Puerta 1 Hoja - Grupo 1</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>303</v>
+      </c>
+      <c r="D277" t="n">
+        <v>227.25</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>MQ-ABA-2</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Mosquitera Abatible Puerta 2 Hojas - Grupo 1</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>605</v>
+      </c>
+      <c r="D278" t="n">
+        <v>453.75</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>MQ-FIJ-1</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Mosquitera Fija con Marco - Grupo 1</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>38</v>
+      </c>
+      <c r="D279" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>MQ-COR-1</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Mosquitera Corredera Perfil Curvo - Grupo 1</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>45</v>
+      </c>
+      <c r="D280" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>MQ-EXP-01</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Carta de Colores Mosquiflex</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>10</v>
+      </c>
+      <c r="D281" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>MQ-EXP-02</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Expositor Personalizable Mosquiflex</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>590</v>
+      </c>
+      <c r="D282" t="n">
+        <v>442.5</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>MQ-03-018</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>1,45 3</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D283" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>MQ-04-019</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>1,45</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D284" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>MQ-04-020</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>1,45</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D285" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>MQ-04-021</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>1,45</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D286" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>MQ-07-022</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Enrollable Puerta ¡La más moderna! La Plisada sin plisar. Dispone de un perfil fijo de aluminio en el cual se aloja un eje con la malla enrollada. Novedoso sistema para instalación en puertas de paso frecuente, con un carril inferior de reducidas dimensiones. Disponible en la versión “Puerta</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D287" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>MQ-07-023</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Ancho</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>MQ-11-024</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>3,1 cm. 4,8 cm. 4,8 cm. 3,1 cm. 2,2 cm. cm. cm.</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="D289" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>MQ-11-025</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>3,1 cm. 4,8 cm. 4,8 cm. 3,1 cm. 2,2 cm. cm. cm. 0,7 cm. 1,88 3,6 MALLA EN COLOR NEGRO Precios Ancho</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>1</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>MQ-13-026</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>ncho</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>MQ-16-027</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D292" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>MQ-16-028</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="D293" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>MQ-16-029</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="D294" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>MQ-16-030</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="D295" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>MQ-16-031</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="D296" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>MQ-16-032</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P.</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="D297" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>MQ-16-033</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril -</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D298" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>MQ-16-034</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="D299" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>MQ-16-035</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D300" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>MQ-16-036</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="D301" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>MQ-16-037</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="D302" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>MQ-16-038</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>56.04</v>
+      </c>
+      <c r="D303" t="n">
+        <v>42.03</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>MQ-16-039</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla 56,04 2200 40 Maneta</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D304" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>MQ-16-040</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla 56,04 2200 40 Maneta - 2,40 Plisada 40 Eslabón</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>2</v>
+      </c>
+      <c r="D305" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>MQ-16-041</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla 56,04 2200 40 Maneta - 2,40 Plisada 40 Eslabón - 2,00 Blanco 40 de</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="D306" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>MQ-16-042</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla 56,04 2200 40 Maneta - 2,40 Plisada 40 Eslabón - 2,00 Blanco 40 de - 2,04 Placa Anclaje 5 nº 0,04 Taco</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>MQ-16-043</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla 56,04 2200 40 Maneta - 2,40 Plisada 40 Eslabón - 2,00 Blanco 40 de - 2,04 Placa Anclaje 5 nº 0,04 Taco 0,20 Tornillo 32</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="D308" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>MQ-16-044</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla 56,04 2200 40 Maneta - 2,40 Plisada 40 Eslabón - 2,00 Blanco 40 de - 2,04 Placa Anclaje 5 nº 0,04 Taco 0,20 Tornillo 32 G1= 11,93 G1= 24,90</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D309" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>MQ-16-045</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla 56,04 2200 40 Maneta - 2,40 Plisada 40 Eslabón - 2,00 Blanco 40 de - 2,04 Placa Anclaje 5 nº 0,04 Taco 0,20 Tornillo 32 G1= 11,93 G1= 24,90 2,20 G G2 3= = 1 13 5, ,3 82 5 4,43 G G2 3= = 2 37 2, ,6 66 3 8,44 29,28 1,40 48,60 7,92 3 x</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="D310" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>MQ-17-046</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>ncho</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>MQ-18-047</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>1= 6,07</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="D312" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>MQ-18-048</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>6,19</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D313" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>FLX-VEN-16</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Veneciana Aluminio 16 mm - Colores Básicos</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>35</v>
+      </c>
+      <c r="D314" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>FLX-VEN-25</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Veneciana Aluminio 25 mm - Colores Básicos</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>29</v>
+      </c>
+      <c r="D315" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>FLX-VEN-50</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Veneciana Aluminio 50 mm - Colores Básicos con Cordón</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>42</v>
+      </c>
+      <c r="D316" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>FLX-VEN-50C</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Veneciana Aluminio 50 mm - Colores Básicos con Cinta</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>48</v>
+      </c>
+      <c r="D317" t="n">
+        <v>36</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>FLX-VEN-MAD</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Veneciana Madera 50 mm - Colección Bali / Madeira</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>78</v>
+      </c>
+      <c r="D318" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>FLX-VT-89</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Cortina Vertical 89 mm - Colección Teide / Alcazaba</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>42</v>
+      </c>
+      <c r="D319" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>FLX-VT-127</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Cortina Vertical 127 mm - Colección Teide / Alcazaba</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>38</v>
+      </c>
+      <c r="D320" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>FLX-PLI-01</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Cortina Plisada Premium PLI.01 - Colección 236</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>58</v>
+      </c>
+      <c r="D321" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>FLX-PLI-REV</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Cortina Plisada Repliegue Reversible PLI.02</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>68</v>
+      </c>
+      <c r="D322" t="n">
+        <v>51</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>FLX-PLI-ND</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Cortina Plisada Noche y Día PLI.03</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>85</v>
+      </c>
+      <c r="D323" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>FLX-PLI-MINI</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Cortina Plisada Mini Cristal Accionamiento Manual</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>49</v>
+      </c>
+      <c r="D324" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>FLX-PLE-01</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Cortina Plegable Confeccionada Sistema Plus</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>55</v>
+      </c>
+      <c r="D325" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>FLX-PAN-01</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Panel Deslizante / Japonés - Sistema Básico 3 Vías</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>65</v>
+      </c>
+      <c r="D326" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>FLX-PAN-02</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Panel Deslizante / Japonés - Sistema Motor 4 Vías</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>120</v>
+      </c>
+      <c r="D327" t="n">
+        <v>90</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>FLX-ENR-UNI</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Cortina Enrollable Universal EN.0 (Sin Tejido)</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>28</v>
+      </c>
+      <c r="D328" t="n">
+        <v>21</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>FLX-ENR-SAT</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Cortina Enrollable Screen Satiné 5500</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>63</v>
+      </c>
+      <c r="D329" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>FLX-ENR-CAJ42</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Cortina Enrollable con Cajón de 42 mm</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>72</v>
+      </c>
+      <c r="D330" t="n">
+        <v>54</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>FLX-ENR-CAJ90</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Cortina Enrollable con Cajón de 90 mm</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>98</v>
+      </c>
+      <c r="D331" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>FLX-ENR-ZIP</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Cortina Enrollable Sistema ZIP Guiada</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>135</v>
+      </c>
+      <c r="D332" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>FLX-LM-01</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Cortina Luz Mágica LM.01 Alborada Galería 80</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>88</v>
+      </c>
+      <c r="D333" t="n">
+        <v>66</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>FLX-LM-02</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Cortina Luz Mágica LM.03 Niebla Galería 90</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>96</v>
+      </c>
+      <c r="D334" t="n">
+        <v>72</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>FLX-005-022</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>LTO CORTINA LARGO MANDOS SÓLO EN SISTEMA 50:
+Hasta</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D335" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>FLX-005-023</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>90 41,40</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="D336" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>FLX-005-024</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>iplos de 5 cm. al alza y el mínimo a facturar será</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D337" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>FLX-006-025</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>P
+24 v.
+P
+Superficie máxima</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D338" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>FLX-006-026</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>A MANDO A DISTANCIA
+Ancho mínimo a fabricar:
+Hasta</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D339" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>FLX-008-027</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>riel será siempre 1,3 cm.
+más corto por cada lado.</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>9</v>
+      </c>
+      <c r="D340" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>FLX-008-028</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>TENSOR SUPERIOR / INFERIOR</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>FLX-008-029</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>CABLE ACERO</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>FLX-008-030</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>VARILLA
+FLEXIBLE
+BLANCA
+1,97</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="D343" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>FLX-008-031</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>1,97</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="D344" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>FLX-008-032</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Sólo Gradúa</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D345" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>FLX-009-033</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Ancho mínimo a fabricar:
+Hasta</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D346" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>FLX-009-034</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Ancho mínimo a fabricar:
+Hasta</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D347" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>FLX-009-035</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Ancho mínimo a fabricar:
+Hasta</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D348" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>FLX-009-036</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>4,86
+5
+7,36
+A 2,04
+33,25
+15,69
+15,69</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>FLX-010-037</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>0,53
+0,67
+0,67</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>FLX-013-038</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>riel será siempre 1,3 cm.
+más corto por cada lado.</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>9</v>
+      </c>
+      <c r="D351" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>FLX-013-039</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>riel será siempre 1,7 cm.
+más corto por cada lado.</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D352" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>FLX-013-040</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>CABLE ACERO</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>FLX-015-041</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>CONJUNTO ELEVACIÓN</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="D354" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>FLX-015-042</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>PREPARADO PARA PULSADOR
+Ancho mínimo a fabricar:</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>FLX-015-043</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>DO PARA MANDO A DISTANCIA
+Ancho mínimo a fabricar:</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>FLX-015-044</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>CONJUNTO ELEVACIÓN</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="D357" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>FLX-016-045</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Base 6,24
+I. Madera</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="D358" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>FLX-017-046</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>453,00
+MANDO A DISTANCIA</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>158</v>
+      </c>
+      <c r="D359" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>FLX-021-047</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>ETE DERECHA - IZQUIERDA - CENTRO
+NCO (ANCHO MÁXIMO</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>FLX-021-048</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>GEDOR CORDÓN 2,55
+9,10
+SEGURIDAD INFANTIL:
+RIDAD</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="D361" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>FLX-025-049</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>ZQUIERDA - DERECHA
+- IZQUIERDA
+O DE MANDOS: MÍNIMO</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>FLX-026-050</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>/m2 m2 /</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D363" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>FLX-027-051</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>27,5 cm. TRANSFORMADOR
+SISTEMA MOTOR</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>365</v>
+      </c>
+      <c r="D364" t="n">
+        <v>273.75</v>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>FLX-027-052</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Solo Gradúa</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D365" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>FLX-028-053</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>ejido 89 - 127 Aluminio, PVC
+y Madera y Tejido 250</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>FLX-028-054</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>0,50</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D367" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>FLX-028-055</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>GANCHO
+Tejido 89 - 12
+y Madera</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D368" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>FLX-028-056</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Cuero</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>141.85</v>
+      </c>
+      <c r="D369" t="n">
+        <v>106.39</v>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>FLX-028-057</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Madera</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="D370" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>FLX-036-058</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>ación del tejido conociendo el ancho de la cortina</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D371" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>FLX-036-059</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>ECHA O IZQUIERDA
+- DERECHA
+MANDOS: MÍNIMO</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D372" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>FLX-036-060</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>T.09
+16,50
+39</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="D373" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>FLX-041-061</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>OS: cm.
+4,2
+ALTO CORTINA LARGO MANDOS
+-NEGRO
+Hasta</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D374" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>FLX-042-062</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>ACCIONAMIENTO MANUAL Premium
+(Ancho máximo</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D375" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>FLX-042-063</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>ARADO PARA PULSADOR
+Ancho mínimo a fabricar:
+Hasta</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D376" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>FLX-042-064</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>O MANDO A DISTANCIA
+Ancho mínimo a fabricar:
+Hasta</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D377" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>FLX-042-065</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>1 Ud.
+Ud.</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>74</v>
+      </c>
+      <c r="D378" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>FLX-045-066</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>INACIÓN
+DE. / IZ. Premium Premium DE. Cordón-50
+10</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="D379" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>FLX-053-067</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>remium Cordón PVC Plisada Cordón-50 Cordón/Varilla</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>FLX-055-068</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>xagonal Plus Cordón Monocomando Monocomando
+5uillo</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="D381" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>FLX-057-069</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>VARILLA SISTEMA MANUAL
+MEDIDA MÁXIMO</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D382" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>FLX-061-070</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>instalación DENOMINACIÓN
+MINI plisada MINI
+Ihesiva</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D383" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>FLX-063-071</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>,9 Clip instalación DENOMINACIÓN
+MINI plisada MINI</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D384" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>FLX-071-072</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>al Perfil fijo cristal Cinta adhesiva DENOMINACIÓN</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D385" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>FLX-073-073</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>A CORDÓN ALTO CORTINA LARGO MANDOS
+VER
+ANCHO Hasta</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D386" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>FLX-073-074</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>fa - PLE.05
+17,55 43,00
+Página 80
+15,50</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>42</v>
+      </c>
+      <c r="D387" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>FLX-073-075</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>SOPORTE</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D388" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>FLX-075-076</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>0,89</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D389" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>FLX-078-077</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>ARADO PARA PULSADOR
+Ancho mínimo a fabricar:
+Hasta</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D390" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>FLX-078-078</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>O MANDO A DISTANCIA
+Ancho mínimo a fabricar:
+Hasta</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D391" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>FLX-089-079</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Varilla Mando</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D392" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>FLX-091-080</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Cinta</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D393" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>FLX-092-081</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>X
+PL. 4153
+(Poliéster)
+PL. 4155 Colores especiales</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D394" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>FLX-092-082</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>16,00
+28,00
+ÑO
+25,00</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>20</v>
+      </c>
+      <c r="D395" t="n">
+        <v>15</v>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>FLX-096-083</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>CORTINA COMPLETA
+S
+TARIFA</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>63</v>
+      </c>
+      <c r="D396" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>FLX-096-084</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>CORTADO
+AL ANCHO</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="D397" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>FLX-096-085</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>24,60
+22,20
+13,45
+24,80
+28,45
+21,90
+16,25
+29,20</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="D398" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>FLX-096-086</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>27,30
+20,45
+37,95
+35,20
+33,75</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>43.65</v>
+      </c>
+      <c r="D399" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>FLX-096-087</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>35,20
+55,10
+55,10
+33,05
+28,35
+45,00
+57,10
+45,00</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D400" t="n">
+        <v>42.83</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>FLX-096-088</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>67,20</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="D401" t="n">
+        <v>22.42</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>FLX-096-089</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>41,05</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="D402" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>FLX-096-090</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>43,65
+35,20
+55,20
+29,90</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="D403" t="n">
+        <v>28.46</v>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>FLX-096-091</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>28,35 35,20 270
+14,10 18,55 300
+24,80 31,10 300</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="D404" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>FLX-097-092</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>43 CON
+ACCIONAMIENTO A CADENA
+SIN REDUCTOR</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>120</v>
+      </c>
+      <c r="D405" t="n">
+        <v>90</v>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>FLX-097-093</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>4,5 X 6</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D406" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>FLX-097-094</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>ÓPICO</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D407" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>FLX-097-095</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>PERFIL ADHESIVO 37,24
+TORNILLO 4 x 4 0,48</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>39</v>
+      </c>
+      <c r="D408" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>ml.</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>FLX-099-096</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>4,92</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D409" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>FLX-099-097</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>1,12
+7,92</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="D410" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>FLX-100-098</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>SIN ZIP CON
+AL</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>74</v>
+      </c>
+      <c r="D411" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>FLX-100-099</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>MANIVELA</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="D412" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>FLX-101-100</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>BLANCO
+MANIVELA</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D413" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>FLX-104-101</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Ud.
+3,55
+10,00
+10,00
+8,96
+11,60</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>4</v>
+      </c>
+      <c r="D414" t="n">
+        <v>3</v>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>FLX-118-102</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>A CABLE PARA MOTOR
+A G
+F
+8,4 cm.
+cm.
+ESCUADRA DE 8</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="D415" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>FLX-121-103</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>/Ud.- m.
+Alto cortina</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="D416" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>FLX-121-104</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>1,3 cm.
+cm.
+5,5</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D417" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>FLX-121-105</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>cm.
+6</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D418" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>FLX-122-106</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>toe DENOMINACIÓN
+D D.58 0 0 to R
+D-43 R-1:1,159,76</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D419" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>FLX-122-107</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>0,48 15,68 0,55</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="D420" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>FLX-122-108</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>D-43 R-1:1,159,76
+D-43 R-1:3 19,06
+D-58 R-1:4</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>39.26</v>
+      </c>
+      <c r="D421" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>FLX-122-109</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>4,5X6 0,82 3,55 Cerrada 1,00 4,45 Cerrada 1,50</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="D422" t="n">
+        <v>4</v>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>FLX-122-110</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>d Ma up eta lld eor DENOMINACIÓN
+R to M to 0cho
+9e</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="D423" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>FLX-122-111</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>0,97 21,30 24,66</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="D424" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>FLX-127-112</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>f j oi ól nC R i 1e e1r c0r te o DENOMINACIÓN E je</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="D425" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>FLX-127-113</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>9,13 19,72 0,97</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="D426" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>FLX-127-114</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>4,5X6 0,82 3,55 Cerrada 1,00 4,45 Cerrada 1,50</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="D427" t="n">
+        <v>4</v>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>FLX-127-115</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>/125
+. .78 0 R o o to
+110
+48,75 34,52 42,33 55,58</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="D428" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>FLX-127-116</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>26,2878,80 2,08</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D429" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>FLX-132-117</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>vf j oi ól nC R 1ie e2r c5r te o DENOMINACIÓN E je</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="D430" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>FLX-132-118</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>9,13 0,97 5,36</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="D431" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>FLX-132-119</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>4,5X6 0,82 3,55 Cerrada 1,00 4,45 Cerrada 1,50</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="D432" t="n">
+        <v>4</v>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>FLX-132-120</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>70 78 (Juego) 110/125 Curvo Recto Curvo Recto
+125</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="D433" t="n">
+        <v>36.56</v>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>FLX-132-121</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>78
+5,91 7,69
+Corona
+6,03</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="D434" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>FLX-132-122</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>26,2878,80 2,08</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D435" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>FLX-140-123</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Tornillo 2,9x9,5 DENOMINACIÓN
+DS DS DS DS
+25,23</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D436" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>FLX-140-124</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Cadena
+Pequeño Mediano Grande Medio Fuerte SIM SIM</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>74.03</v>
+      </c>
+      <c r="D437" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>FLX-142-125</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>X PL. 4153
+(Poliéster)
+PL. 4155
+Colores especiales</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D438" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>FLX-150-126</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>RADIO
+AM35 PLUS L 6/18 D.43/58 6 18 14,8 36 W. 40</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>329</v>
+      </c>
+      <c r="D439" t="n">
+        <v>246.75</v>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>FLX-151-127</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Blanco: 38,16 Plata:</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="D440" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>FLX-151-128</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Blanco: 33,97 Plata:</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="D441" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>FLX-151-129</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Blanco:11,76
+Plata:</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="D442" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>ud.</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/precios_catalogo.xlsx
+++ b/precios_catalogo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G442"/>
+  <dimension ref="A1:G436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Mosquitera Enrollable Ventana 42 - Grupo 2 (Plata/Bronce/RAL)</t>
+          <t>Mosquitera Enrollable Ventana 42 - Grupo 2 (Plata / Bronce / RAL Estándar)</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Mosquitera Enrollable Ventana 42 - Grupo 3 (Madera)</t>
+          <t>Mosquitera Enrollable Ventana 42 - Grupo 3 (Madera / Foliado)</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -9175,19 +9175,19 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>MQ-ENR-PTA1</t>
+          <t>MQ-ENR-MUE</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Mosquitera Enrollable Puerta Lateral Única - Grupo 1</t>
+          <t>Muelle de retención para Mosquitera Enrollable 42</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="D269" t="n">
-        <v>93.75</v>
+        <v>9</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -9208,19 +9208,19 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>MQ-ENR-PTA2</t>
+          <t>MQ-ENR-AV1</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Mosquitera Enrollable Puerta Lateral Doble - Grupo 1</t>
+          <t>Guías con 1 Felpudo Antiviento (Incremento)</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>230</v>
+        <v>3.8</v>
       </c>
       <c r="D270" t="n">
-        <v>172.5</v>
+        <v>2.85</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -9241,19 +9241,19 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>MQ-PLI-22-1</t>
+          <t>MQ-ENR-AV2</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Mosquitera Plisada 22 Puerta Única - Grupo 1</t>
+          <t>Guías con 2 Felpudos Antiviento (Incremento)</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>135</v>
+        <v>7.6</v>
       </c>
       <c r="D271" t="n">
-        <v>101.25</v>
+        <v>5.7</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -9274,19 +9274,19 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>MQ-PLI-22-2</t>
+          <t>MQ-ENR-DAV1</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Mosquitera Plisada 22 Puerta Doble - Grupo 1</t>
+          <t>Guía doble con 1 Felpudo Antiviento (Incremento)</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>245</v>
+        <v>3.8</v>
       </c>
       <c r="D272" t="n">
-        <v>183.75</v>
+        <v>2.85</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -9307,19 +9307,19 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>MQ-PLI-22-REV</t>
+          <t>MQ-ENR-DAV2</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Mosquitera Plisada 22 Reversible - Grupo 1</t>
+          <t>Guía doble con 2 Felpudos Antiviento (Incremento)</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>155</v>
+        <v>7.6</v>
       </c>
       <c r="D273" t="n">
-        <v>116.25</v>
+        <v>5.7</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -9340,19 +9340,19 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>MQ-PLI-22-VEN</t>
+          <t>MQ-ENR-TET20</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Mosquitera Plisada 22 Ventana - Grupo 1</t>
+          <t>Malla TETUG 20-1400 enrollada en eje</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>85</v>
+        <v>28.5</v>
       </c>
       <c r="D274" t="n">
-        <v>63.75</v>
+        <v>21.38</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -9373,19 +9373,19 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>MQ-PLI-40-1</t>
+          <t>MQ-ENR-TET25</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Mosquitera Plisada 40 Puerta Única - Grupo 1</t>
+          <t>Malla TETUG 25-1400 enrollada en eje</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>326</v>
+        <v>33.2</v>
       </c>
       <c r="D275" t="n">
-        <v>244.5</v>
+        <v>24.9</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -9406,19 +9406,19 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>MQ-PLI-40-2</t>
+          <t>MQ-ENR-TET23</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Mosquitera Plisada 40 Puerta Doble - Grupo 1</t>
+          <t>Malla TETUG 23-1400 Enrollable Puerta</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>653</v>
+        <v>37.12</v>
       </c>
       <c r="D276" t="n">
-        <v>489.75</v>
+        <v>27.84</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -9439,19 +9439,19 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>MQ-ABA-1</t>
+          <t>MQ-ENR-PTA1</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Mosquitera Abatible Puerta 1 Hoja - Grupo 1</t>
+          <t>Mosquitera Enrollable Puerta Lateral Única - Grupo 1</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>303</v>
+        <v>125</v>
       </c>
       <c r="D277" t="n">
-        <v>227.25</v>
+        <v>93.75</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -9472,19 +9472,19 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MQ-ABA-2</t>
+          <t>MQ-ENR-PTA2</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Mosquitera Abatible Puerta 2 Hojas - Grupo 1</t>
+          <t>Mosquitera Enrollable Puerta Lateral Doble - Grupo 1</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>605</v>
+        <v>230</v>
       </c>
       <c r="D278" t="n">
-        <v>453.75</v>
+        <v>172.5</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -9505,23 +9505,23 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>MQ-FIJ-1</t>
+          <t>MQ-CMP-PTA01</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Mosquitera Fija con Marco - Grupo 1</t>
+          <t>Perfil Cierre Imán Enrollable Puerta</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>38</v>
+        <v>11.47</v>
       </c>
       <c r="D279" t="n">
-        <v>28.5</v>
+        <v>8.6</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -9538,23 +9538,23 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MQ-COR-1</t>
+          <t>MQ-CMP-PTA02</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Mosquitera Corredera Perfil Curvo - Grupo 1</t>
+          <t>Eslabón Antiviento Enrollable Puerta (Juego)</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>45</v>
+        <v>7.56</v>
       </c>
       <c r="D280" t="n">
-        <v>33.75</v>
+        <v>5.67</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -9571,19 +9571,19 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>MQ-EXP-01</t>
+          <t>MQ-CMP-PTA03</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Carta de Colores Mosquiflex</t>
+          <t>Cadena Inferior Enrollable Puerta</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>10</v>
+        <v>49.08</v>
       </c>
       <c r="D281" t="n">
-        <v>7.5</v>
+        <v>36.81</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -9604,23 +9604,23 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>MQ-EXP-02</t>
+          <t>MQ-CMP-PTA04</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Expositor Personalizable Mosquiflex</t>
+          <t>Imán Perfil Móvil Enrollable Puerta</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>590</v>
+        <v>2.2</v>
       </c>
       <c r="D282" t="n">
-        <v>442.5</v>
+        <v>1.65</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -9637,23 +9637,23 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>MQ-03-018</t>
+          <t>MQ-CMP-PTA05</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>1,45 3</t>
+          <t>Imán Perfil Cierre Enrollable Puerta</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>1.6</v>
+        <v>2.76</v>
       </c>
       <c r="D283" t="n">
-        <v>1.2</v>
+        <v>2.07</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -9661,28 +9661,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>MQ-04-019</t>
+          <t>MQ-CMP-PTA06</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>Portaimán Enrollable Puerta</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>1.6</v>
+        <v>5.77</v>
       </c>
       <c r="D284" t="n">
-        <v>1.2</v>
+        <v>4.33</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -9690,28 +9694,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>MQ-04-020</t>
+          <t>MQ-CMP-PTA07</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>Hilo Trenzado Negro Enrollable Puerta</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="D285" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -9719,28 +9727,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>MQ-04-021</t>
+          <t>MQ-CMP-PTA08</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>Carril Inferior Enrollable Puerta</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>1.6</v>
+        <v>14.57</v>
       </c>
       <c r="D286" t="n">
-        <v>1.2</v>
+        <v>10.93</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -9748,24 +9760,28 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>MQ-07-022</t>
+          <t>MQ-CMP-PTA09</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Enrollable Puerta ¡La más moderna! La Plisada sin plisar. Dispone de un perfil fijo de aluminio en el cual se aloja un eje con la malla enrollada. Novedoso sistema para instalación en puertas de paso frecuente, con un carril inferior de reducidas dimensiones. Disponible en la versión “Puerta</t>
+          <t>Perfil Móvil Enrollable Puerta (G1 Blanco)</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>2.8</v>
+        <v>38.18</v>
       </c>
       <c r="D287" t="n">
-        <v>2.1</v>
+        <v>28.63</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -9777,28 +9793,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>MQ-07-023</t>
+          <t>MQ-CMP-PTA10</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Ancho</t>
+          <t>Carril Superior Enrollable Puerta (G1 Blanco)</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>0.8</v>
+        <v>28.84</v>
       </c>
       <c r="D288" t="n">
-        <v>0.6</v>
+        <v>21.63</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -9806,28 +9826,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>MQ-11-024</t>
+          <t>MQ-CMP-PTA11</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>3,1 cm. 4,8 cm. 4,8 cm. 3,1 cm. 2,2 cm. cm. cm.</t>
+          <t>Perfil Fijo Enrollable Puerta (G1 Blanco)</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>1.88</v>
+        <v>31.97</v>
       </c>
       <c r="D289" t="n">
-        <v>1.41</v>
+        <v>23.98</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -9835,28 +9859,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>MQ-11-025</t>
+          <t>MQ-CMP-PTA12</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>3,1 cm. 4,8 cm. 4,8 cm. 3,1 cm. 2,2 cm. cm. cm. 0,7 cm. 1,88 3,6 MALLA EN COLOR NEGRO Precios Ancho</t>
+          <t>Fleje Enrollable Puerta</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D290" t="n">
-        <v>0.75</v>
+        <v>5.25</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -9864,24 +9892,28 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>MQ-13-026</t>
+          <t>MQ-CMP-PTA13</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>ncho</t>
+          <t>Kit Felpudo 4,8 x 19 mm Enrollable Puerta</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>0.8</v>
+        <v>85.88</v>
       </c>
       <c r="D291" t="n">
-        <v>0.6</v>
+        <v>64.41</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -9893,28 +9925,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>MQ-16-027</t>
+          <t>MQ-PLI-22-1</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40</t>
+          <t>Mosquitera Plisada 22 Puerta Única - Grupo 1</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>23.9</v>
+        <v>135</v>
       </c>
       <c r="D292" t="n">
-        <v>17.92</v>
+        <v>101.25</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -9922,28 +9958,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>MQ-16-028</t>
+          <t>MQ-PLI-22-2</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90</t>
+          <t>Mosquitera Plisada 22 Puerta Doble - Grupo 1</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>27.1</v>
+        <v>245</v>
       </c>
       <c r="D293" t="n">
-        <v>20.33</v>
+        <v>183.75</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -9951,28 +9991,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>MQ-16-029</t>
+          <t>MQ-PLI-22-REV</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40</t>
+          <t>Mosquitera Plisada 22 Reversible - Grupo 1</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>1.44</v>
+        <v>155</v>
       </c>
       <c r="D294" t="n">
-        <v>1.08</v>
+        <v>116.25</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -9980,28 +10024,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>MQ-16-030</t>
+          <t>MQ-PLI-22-VEN</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera</t>
+          <t>Mosquitera Plisada 22 Ventana - Grupo 1</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>31.95</v>
+        <v>85</v>
       </c>
       <c r="D295" t="n">
-        <v>23.96</v>
+        <v>63.75</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -10009,24 +10057,28 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>MQ-16-031</t>
+          <t>MQ-CMP-PL22-01</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r</t>
+          <t>Perfil Fijo Plisada 22 (G1 Blanco)</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>42.3</v>
+        <v>12.37</v>
       </c>
       <c r="D296" t="n">
-        <v>31.72</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -10038,24 +10090,28 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>MQ-16-032</t>
+          <t>MQ-CMP-PL22-02</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P.</t>
+          <t>Carril Superior Plisada 22 (G1 Blanco)</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>19.1</v>
+        <v>13.64</v>
       </c>
       <c r="D297" t="n">
-        <v>14.33</v>
+        <v>10.23</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -10067,24 +10123,28 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>MQ-16-033</t>
+          <t>MQ-CMP-PL22-03</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril -</t>
+          <t>Perfil Móvil Plisada 22 (G1 Blanco)</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>1.52</v>
+        <v>21.98</v>
       </c>
       <c r="D298" t="n">
-        <v>1.14</v>
+        <v>16.48</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -10096,24 +10156,28 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>MQ-16-034</t>
+          <t>MQ-CMP-PL22-04</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón</t>
+          <t>Carril Inferior Aluminio Negro Plisada 22</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>1.65</v>
+        <v>6.95</v>
       </c>
       <c r="D299" t="n">
-        <v>1.24</v>
+        <v>5.21</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -10125,24 +10189,28 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr"/>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>MQ-16-035</t>
+          <t>MQ-CMP-PL22-05</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones</t>
+          <t>Adhesivo Carril Inferior Plisada 22</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="D300" t="n">
-        <v>4.35</v>
+        <v>1.5</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -10154,28 +10222,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>MQ-16-036</t>
+          <t>MQ-CMP-PL22-06</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40</t>
+          <t>Clip Hilo Plisada 22 / 40</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="D301" t="n">
-        <v>1.59</v>
+        <v>0.78</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -10183,24 +10255,28 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr"/>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>MQ-16-037</t>
+          <t>MQ-CMP-PL22-07</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo</t>
+          <t>Hilo Negro Plisada 22 / 40</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>62.56</v>
+        <v>1.88</v>
       </c>
       <c r="D302" t="n">
-        <v>46.92</v>
+        <v>1.41</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -10212,24 +10288,28 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>MQ-16-038</t>
+          <t>MQ-CMP-PL22-08</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla</t>
+          <t>Imán Perfil Fijo Plisada 22</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>56.04</v>
+        <v>2.97</v>
       </c>
       <c r="D303" t="n">
-        <v>42.03</v>
+        <v>2.23</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -10241,24 +10321,28 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>MQ-16-039</t>
+          <t>MQ-CMP-PL22-09</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla 56,04 2200 40 Maneta</t>
+          <t>Imán Perfil Móvil Plisada 22</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="D304" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -10270,28 +10354,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>MQ-16-040</t>
+          <t>MQ-CMP-PL22-10</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla 56,04 2200 40 Maneta - 2,40 Plisada 40 Eslabón</t>
+          <t>Malla Plisada 22 - 2400 mm</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>2</v>
+        <v>50.64</v>
       </c>
       <c r="D305" t="n">
-        <v>1.5</v>
+        <v>37.98</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -10299,28 +10387,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr"/>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>MQ-16-041</t>
+          <t>MQ-CMP-PL22-11</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla 56,04 2200 40 Maneta - 2,40 Plisada 40 Eslabón - 2,00 Blanco 40 de</t>
+          <t>Malla Plisada 22 - 3000 mm</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>2.04</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D306" t="n">
-        <v>1.53</v>
+        <v>58.05</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -10328,28 +10420,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>MQ-16-042</t>
+          <t>MQ-CMP-PL22-12</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla 56,04 2200 40 Maneta - 2,40 Plisada 40 Eslabón - 2,00 Blanco 40 de - 2,04 Placa Anclaje 5 nº 0,04 Taco</t>
+          <t>Lámina Fijación Malla 22</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>0.2</v>
+        <v>3.88</v>
       </c>
       <c r="D307" t="n">
-        <v>0.15</v>
+        <v>2.91</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -10357,24 +10453,28 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>MQ-16-043</t>
+          <t>MQ-CMP-PL22-13</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla 56,04 2200 40 Maneta - 2,40 Plisada 40 Eslabón - 2,00 Blanco 40 de - 2,04 Placa Anclaje 5 nº 0,04 Taco 0,20 Tornillo 32</t>
+          <t>Perfil Instalación Frontal Plisada 22 (G1 Blanco)</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>11.93</v>
+        <v>22.95</v>
       </c>
       <c r="D308" t="n">
-        <v>8.949999999999999</v>
+        <v>17.21</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -10386,28 +10486,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr"/>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>MQ-16-044</t>
+          <t>MQ-PLI-40-1</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla 56,04 2200 40 Maneta - 2,40 Plisada 40 Eslabón - 2,00 Blanco 40 de - 2,04 Placa Anclaje 5 nº 0,04 Taco 0,20 Tornillo 32 G1= 11,93 G1= 24,90</t>
+          <t>Mosquitera Plisada 40 Puerta Única - Grupo 1</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2.2</v>
+        <v>326</v>
       </c>
       <c r="D309" t="n">
-        <v>1.65</v>
+        <v>244.5</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -10415,28 +10519,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr"/>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>MQ-16-045</t>
+          <t>MQ-PLI-40-2</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>CaT na top na e ra Clip Hilo Clip Hilo 40 Lamina Cantonera CaT na top na e ra Tornillo 3x12 Perfil Superior 22 / 40 De / Iz Fijación Superior Superior Tapa Fijo - 40 P. Móvil - 40 M. 20/40 P. Fijo - 40 P. Fijo - 40 Superior - 40 G1=23,90 G2=27,10 40 1,44 1,04 1,78 3,88 7,92 1,44 0,20 Cantonera G3=31,95 - o r G4=42,30 Mp óe vi r li 8,92 Su P. 40 G1=19,10 G2=21,38 G3=25,51 G4=34,63 Carril Superior - 40 Carril - Superior 1,52 Tapa 40 Eslabón - 1,65 Gancho 3 Eslabones Cadena 5,80 Eslabón 40 - 2,12 Rojo 62,56 2600 Plisada Malla 56,04 2200 40 Maneta - 2,40 Plisada 40 Eslabón - 2,00 Blanco 40 de - 2,04 Placa Anclaje 5 nº 0,04 Taco 0,20 Tornillo 32 G1= 11,93 G1= 24,90 2,20 G G2 3= = 1 13 5, ,3 82 5 4,43 G G2 3= = 2 37 2, ,6 66 3 8,44 29,28 1,40 48,60 7,92 3 x</t>
+          <t>Mosquitera Plisada 40 Puerta Doble - Grupo 1</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>21.43</v>
+        <v>653</v>
       </c>
       <c r="D310" t="n">
-        <v>16.07</v>
+        <v>489.75</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -10444,28 +10552,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>MQ-17-046</t>
+          <t>MQ-CMP-PL40-01</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>ncho</t>
+          <t>Perfil Fijo Plisada 40 (G1 Blanco)</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>0.6</v>
+        <v>23.9</v>
       </c>
       <c r="D311" t="n">
-        <v>0.45</v>
+        <v>17.92</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -10473,28 +10585,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>MQ-18-047</t>
+          <t>MQ-CMP-PL40-02</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>1= 6,07</t>
+          <t>Perfil Móvil Plisada 40 (G1 Blanco)</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>8.67</v>
+        <v>24.9</v>
       </c>
       <c r="D312" t="n">
-        <v>6.5</v>
+        <v>18.67</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -10502,28 +10618,32 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>MQ-18-048</t>
+          <t>MQ-CMP-PL40-03</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>6,19</t>
+          <t>Carril Superior Plisada 40 (G1 Blanco)</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>8.699999999999999</v>
+        <v>19.1</v>
       </c>
       <c r="D313" t="n">
-        <v>6.52</v>
+        <v>14.33</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -10531,434 +10651,490 @@
           <t>Mosquiflex</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>FLX-VEN-16</t>
+          <t>MQ-CMP-PL40-04</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Veneciana Aluminio 16 mm - Colores Básicos</t>
+          <t>Perfil Cierre Imán Plisada 40</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>35</v>
+        <v>11.93</v>
       </c>
       <c r="D314" t="n">
-        <v>26.25</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>FLX-VEN-25</t>
+          <t>MQ-CMP-PL40-05</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Veneciana Aluminio 25 mm - Colores Básicos</t>
+          <t>Porta Imán Plisada 40</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>29</v>
+        <v>4.43</v>
       </c>
       <c r="D315" t="n">
-        <v>21.75</v>
+        <v>3.32</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>FLX-VEN-50</t>
+          <t>MQ-CMP-PL40-06</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Veneciana Aluminio 50 mm - Colores Básicos con Cordón</t>
+          <t>Carril Inferior Gris Adhesivo Plisada 40</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>42</v>
+        <v>29.28</v>
       </c>
       <c r="D316" t="n">
-        <v>31.5</v>
+        <v>21.96</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>FLX-VEN-50C</t>
+          <t>MQ-CMP-PL40-07</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Veneciana Aluminio 50 mm - Colores Básicos con Cinta</t>
+          <t>Cadena 58 Eslabones Plisada 40</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="D317" t="n">
-        <v>36</v>
+        <v>36.45</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>FLX-VEN-MAD</t>
+          <t>MQ-CMP-PL40-08</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Veneciana Madera 50 mm - Colección Bali / Madeira</t>
+          <t>Cadena 3 Eslabones Plisada 40</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>78</v>
+        <v>5.8</v>
       </c>
       <c r="D318" t="n">
-        <v>58.5</v>
+        <v>4.35</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>FLX-VT-89</t>
+          <t>MQ-CMP-PL40-09</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Cortina Vertical 89 mm - Colección Teide / Alcazaba</t>
+          <t>Eslabón Reversible Plisada 40</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>42</v>
+        <v>1.4</v>
       </c>
       <c r="D319" t="n">
-        <v>31.5</v>
+        <v>1.05</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>FLX-VT-127</t>
+          <t>MQ-CMP-PL40-10</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Cortina Vertical 127 mm - Colección Teide / Alcazaba</t>
+          <t>Eslabón Gancho Plisada 40</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>38</v>
+        <v>1.65</v>
       </c>
       <c r="D320" t="n">
-        <v>28.5</v>
+        <v>1.24</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>FLX-PLI-01</t>
+          <t>MQ-CMP-PL40-11</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Cortina Plisada Premium PLI.01 - Colección 236</t>
+          <t>Eslabón Rojo Plisada 40</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>58</v>
+        <v>2.12</v>
       </c>
       <c r="D321" t="n">
-        <v>43.5</v>
+        <v>1.59</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>FLX-PLI-REV</t>
+          <t>MQ-CMP-PL40-12</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Cortina Plisada Repliegue Reversible PLI.02</t>
+          <t>Eslabón Blanco Plisada 40</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D322" t="n">
-        <v>51</v>
+        <v>1.5</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>FLX-PLI-ND</t>
+          <t>MQ-CMP-PL40-13</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Cortina Plisada Noche y Día PLI.03</t>
+          <t>Maneta Plisada 40</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>85</v>
+        <v>2.4</v>
       </c>
       <c r="D323" t="n">
-        <v>63.75</v>
+        <v>1.8</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>FLX-PLI-MINI</t>
+          <t>MQ-CMP-PL40-14</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Cortina Plisada Mini Cristal Accionamiento Manual</t>
+          <t>Malla Plisada 40 - 2200 mm</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>49</v>
+        <v>56.04</v>
       </c>
       <c r="D324" t="n">
-        <v>36.75</v>
+        <v>42.03</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>FLX-PLE-01</t>
+          <t>MQ-CMP-PL40-15</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Cortina Plegable Confeccionada Sistema Plus</t>
+          <t>Malla Plisada 40 - 2600 mm</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>55</v>
+        <v>62.56</v>
       </c>
       <c r="D325" t="n">
-        <v>41.25</v>
+        <v>46.92</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>FLX-PAN-01</t>
+          <t>MQ-CMP-PL40-16</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Panel Deslizante / Japonés - Sistema Básico 3 Vías</t>
+          <t>Cantonera Superior P. Móvil 40</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>65</v>
+        <v>8.92</v>
       </c>
       <c r="D326" t="n">
-        <v>48.75</v>
+        <v>6.69</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>FLX-PAN-02</t>
+          <t>MQ-CMP-PL40-17</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Panel Deslizante / Japonés - Sistema Motor 4 Vías</t>
+          <t>Cantonera Superior P. Fijo 40</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>120</v>
+        <v>7.92</v>
       </c>
       <c r="D327" t="n">
-        <v>90</v>
+        <v>5.94</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Flexol</t>
+          <t>Mosquiflex</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
+          <t>extracted_images/motor_p1_600500037.png</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>FLX-ENR-UNI</t>
+          <t>MQ-CMP-PL40-18</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Cortina Enrollable Universal EN.0 (Sin Tejido)</t>
+          <t>Cantonera Inferior P. Móvil 40</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>28</v>
+        <v>8.44</v>
       </c>
       <c r="D328" t="n">
-        <v>21</v>
+        <v>6.33</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -10967,231 +11143,262 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>FLX-ENR-SAT</t>
+          <t>MQ-CMP-PL40-19</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Cortina Enrollable Screen Satiné 5500</t>
+          <t>Cantonera Inferior P. Fijo 40</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>63</v>
+        <v>7.92</v>
       </c>
       <c r="D329" t="n">
-        <v>47.25</v>
+        <v>5.94</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>FLX-ENR-CAJ42</t>
+          <t>MQ-ABA-1</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Cortina Enrollable con Cajón de 42 mm</t>
+          <t>Mosquitera Abatible Puerta 1 Hoja - Grupo 1 (Blanco)</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>72</v>
+        <v>303</v>
       </c>
       <c r="D330" t="n">
-        <v>54</v>
+        <v>227.25</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>FLX-ENR-CAJ90</t>
+          <t>MQ-ABA-2</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Cortina Enrollable con Cajón de 90 mm</t>
+          <t>Mosquitera Abatible Puerta 2 Hojas - Grupo 1 (Blanco)</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>98</v>
+        <v>605</v>
       </c>
       <c r="D331" t="n">
-        <v>73.5</v>
+        <v>453.75</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>FLX-ENR-ZIP</t>
+          <t>MQ-CMP-AB01</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Cortina Enrollable Sistema ZIP Guiada</t>
+          <t>Perfil Marco Abatible (G1 Blanco)</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>135</v>
+        <v>18.5</v>
       </c>
       <c r="D332" t="n">
-        <v>101.25</v>
+        <v>13.88</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>FLX-LM-01</t>
+          <t>MQ-CMP-AB02</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Cortina Luz Mágica LM.01 Alborada Galería 80</t>
+          <t>Perfil Hoja Abatible (G1 Blanco)</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>88</v>
+        <v>21.2</v>
       </c>
       <c r="D333" t="n">
-        <v>66</v>
+        <v>15.9</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>FLX-LM-02</t>
+          <t>MQ-CMP-AB03</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Cortina Luz Mágica LM.03 Niebla Galería 90</t>
+          <t>Perfil Encuentro Abatible 2 Hojas (G1 Blanco)</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>96</v>
+        <v>13.27</v>
       </c>
       <c r="D334" t="n">
-        <v>72</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>FLX-005-022</t>
+          <t>MQ-CMP-AB04</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>LTO CORTINA LARGO MANDOS SÓLO EN SISTEMA 50:
-Hasta</t>
+          <t>Perfil Travesaño Abatible (G1 Blanco)</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>1.6</v>
+        <v>10.93</v>
       </c>
       <c r="D335" t="n">
-        <v>1.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>FLX-005-023</t>
+          <t>MQ-CMP-AB05</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>90 41,40</t>
+          <t>Bisagra con Muelle de Retorno Abatible</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>57.5</v>
+        <v>12.8</v>
       </c>
       <c r="D336" t="n">
-        <v>43.12</v>
+        <v>9.6</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -11200,178 +11407,196 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>FLX-005-024</t>
+          <t>MQ-FIJ-1</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>iplos de 5 cm. al alza y el mínimo a facturar será</t>
+          <t>Mosquitera Fija con Marco - Grupo 1 (Blanco)</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>1.5</v>
+        <v>38</v>
       </c>
       <c r="D337" t="n">
-        <v>1.12</v>
+        <v>28.5</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>FLX-006-025</t>
+          <t>MQ-FIJ-2</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>P
-24 v.
-P
-Superficie máxima</t>
+          <t>Mosquitera Fija con Marco - Grupo 2 (Plata / RAL)</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>4.1</v>
+        <v>44</v>
       </c>
       <c r="D338" t="n">
-        <v>3.07</v>
+        <v>33</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>FLX-006-026</t>
+          <t>MQ-COR-1</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>A MANDO A DISTANCIA
-Ancho mínimo a fabricar:
-Hasta</t>
+          <t>Mosquitera Corredera Perfil Curvo - Grupo 1 (Blanco)</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>2.2</v>
+        <v>45</v>
       </c>
       <c r="D339" t="n">
-        <v>1.65</v>
+        <v>33.75</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>FLX-008-027</t>
+          <t>MQ-COR-2</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>riel será siempre 1,3 cm.
-más corto por cada lado.</t>
+          <t>Mosquitera Corredera Perfil Curvo - Grupo 2 (Plata / RAL)</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D340" t="n">
-        <v>6.75</v>
+        <v>39</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>FLX-008-028</t>
+          <t>MQ-CMP-CR01</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>TENSOR SUPERIOR / INFERIOR</t>
+          <t>Marco Corredera Guía Z - Grupo 1 (Blanco)</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>0.6899999999999999</v>
+        <v>18.6</v>
       </c>
       <c r="D341" t="n">
-        <v>0.52</v>
+        <v>13.95</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>FLX-008-029</t>
+          <t>MQ-CMP-CR02</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>CABLE ACERO</t>
+          <t>Rodamientos Rueda Corredera (Juego)</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>0.93</v>
+        <v>4.8</v>
       </c>
       <c r="D342" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -11380,59 +11605,64 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>FLX-008-030</t>
+          <t>MQ-INC-TRAV</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>VARILLA
-FLEXIBLE
-BLANCA
-1,97</t>
+          <t>Travesaño Adicional Mosquitera (Incremento)</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>3.79</v>
+        <v>23.8</v>
       </c>
       <c r="D343" t="n">
-        <v>2.84</v>
+        <v>17.85</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>FLX-008-031</t>
+          <t>MQ-INC-IRR</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>Forma Irregular / Plantilla (Incremento)</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>3.79</v>
+        <v>27</v>
       </c>
       <c r="D344" t="n">
-        <v>2.84</v>
+        <v>20.25</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -11441,27 +11671,31 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>FLX-008-032</t>
+          <t>MQ-INC-MEDP</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Sólo Gradúa</t>
+          <t>Medio Punto / Arco Curva Monoradio (Incremento)</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>22.3</v>
+        <v>100</v>
       </c>
       <c r="D345" t="n">
-        <v>16.73</v>
+        <v>75</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -11470,28 +11704,31 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>FLX-009-033</t>
+          <t>MQ-INC-BUEY</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Ancho mínimo a fabricar:
-Hasta</t>
+          <t>Ojo de Buey / Curva Multiradio (Incremento)</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>2.2</v>
+        <v>250</v>
       </c>
       <c r="D346" t="n">
-        <v>1.65</v>
+        <v>187.5</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -11500,28 +11737,31 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>FLX-009-034</t>
+          <t>MQ-EXP-01</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Ancho mínimo a fabricar:
-Hasta</t>
+          <t>Carta de Colores Mosquiflex</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="D347" t="n">
-        <v>1.65</v>
+        <v>7.5</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -11530,28 +11770,31 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>FLX-009-035</t>
+          <t>MQ-EXP-02</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Ancho mínimo a fabricar:
-Hasta</t>
+          <t>Expositor Personalizable Mosquiflex</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>2.2</v>
+        <v>590</v>
       </c>
       <c r="D348" t="n">
-        <v>1.65</v>
+        <v>442.5</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -11560,37 +11803,35 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr"/>
+          <t>Mosquiflex</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500037.png</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>FLX-009-036</t>
+          <t>FLX-VEN-16</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>4,86
-5
-7,36
-A 2,04
-33,25
-15,69
-15,69</t>
+          <t>Veneciana Aluminio 16 mm - Colores Básicos</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>0.49</v>
+        <v>35</v>
       </c>
       <c r="D349" t="n">
-        <v>0.37</v>
+        <v>26.25</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -11598,30 +11839,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>FLX-010-037</t>
+          <t>FLX-VEN-25</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>0,53
-0,67
-0,67</t>
+          <t>Veneciana Aluminio 25 mm - Colores Básicos</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>0.67</v>
+        <v>29</v>
       </c>
       <c r="D350" t="n">
-        <v>0.5</v>
+        <v>21.75</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -11629,29 +11872,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>FLX-013-038</t>
+          <t>FLX-VEN-50</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>riel será siempre 1,3 cm.
-más corto por cada lado.</t>
+          <t>Veneciana Aluminio 50 mm - Colores Básicos con Cordón</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D351" t="n">
-        <v>6.75</v>
+        <v>31.5</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -11659,29 +11905,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>FLX-013-039</t>
+          <t>FLX-VEN-50C</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>riel será siempre 1,7 cm.
-más corto por cada lado.</t>
+          <t>Veneciana Aluminio 50 mm - Colores Básicos con Cinta</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>22.8</v>
+        <v>48</v>
       </c>
       <c r="D352" t="n">
-        <v>17.1</v>
+        <v>36</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -11689,28 +11938,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>FLX-013-040</t>
+          <t>FLX-VEN-MAD</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>CABLE ACERO</t>
+          <t>Veneciana Madera 50 mm - Colección Madeira / Bali</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>0.93</v>
+        <v>78</v>
       </c>
       <c r="D353" t="n">
-        <v>0.7</v>
+        <v>58.5</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -11718,28 +11971,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>FLX-015-041</t>
+          <t>FLX-VEN-MAD2</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>CONJUNTO ELEVACIÓN</t>
+          <t>Veneciana Madera 50 mm - Colección Ceylan / Seychelles</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>38.45</v>
+        <v>88</v>
       </c>
       <c r="D354" t="n">
-        <v>28.84</v>
+        <v>66</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -11747,29 +12004,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr"/>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>FLX-015-042</t>
+          <t>FLX-CMP-VN01</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PREPARADO PARA PULSADOR
-Ancho mínimo a fabricar:</t>
+          <t>Cabezal de Aluminio 25 mm</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>0.59</v>
+        <v>4.86</v>
       </c>
       <c r="D355" t="n">
-        <v>0.44</v>
+        <v>3.65</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -11777,29 +12037,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr"/>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>FLX-015-043</t>
+          <t>FLX-CMP-VN02</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>DO PARA MANDO A DISTANCIA
-Ancho mínimo a fabricar:</t>
+          <t>Cabezal de Aluminio 50 mm</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>0.65</v>
+        <v>7.36</v>
       </c>
       <c r="D356" t="n">
-        <v>0.49</v>
+        <v>5.52</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -11807,28 +12070,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>FLX-015-044</t>
+          <t>FLX-CMP-VN03</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>CONJUNTO ELEVACIÓN</t>
+          <t>Terminal Inferior Aluminio 25 mm</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>38.45</v>
+        <v>2.04</v>
       </c>
       <c r="D357" t="n">
-        <v>28.84</v>
+        <v>1.53</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -11836,29 +12103,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G357" t="inlineStr"/>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>FLX-016-045</t>
+          <t>FLX-CMP-VN04</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Base 6,24
-I. Madera</t>
+          <t>Terminal Inferior Aluminio 50 mm</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>9.52</v>
+        <v>5.52</v>
       </c>
       <c r="D358" t="n">
-        <v>7.14</v>
+        <v>4.14</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -11866,29 +12136,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>FLX-017-046</t>
+          <t>FLX-CMP-VN05</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>453,00
-MANDO A DISTANCIA</t>
+          <t>Galería Madera G-1 para incrustar en hueco</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>158</v>
+        <v>15.51</v>
       </c>
       <c r="D359" t="n">
-        <v>118.5</v>
+        <v>11.63</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -11896,29 +12169,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr"/>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>FLX-021-047</t>
+          <t>FLX-CMP-VN06</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>ETE DERECHA - IZQUIERDA - CENTRO
-NCO (ANCHO MÁXIMO</t>
+          <t>Galería Madera G-3 en U</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>1.2</v>
+        <v>29.42</v>
       </c>
       <c r="D360" t="n">
-        <v>0.9</v>
+        <v>22.07</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -11926,27 +12202,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr"/>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>FLX-021-048</t>
+          <t>FLX-CMP-VN07</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>GEDOR CORDÓN 2,55
-9,10
-SEGURIDAD INFANTIL:
-RIDAD</t>
+          <t>Maquinilla Freno Cordón 25 mm</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>1.46</v>
+        <v>2.17</v>
       </c>
       <c r="D361" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -11958,26 +12235,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>FLX-025-049</t>
+          <t>FLX-CMP-VN08</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>ZQUIERDA - DERECHA
-- IZQUIERDA
-O DE MANDOS: MÍNIMO</t>
+          <t>Maquinilla Orientador Varilla 25 mm</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>0.75</v>
+        <v>1.78</v>
       </c>
       <c r="D362" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -11989,28 +12268,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr"/>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>FLX-026-050</t>
+          <t>FLX-CMP-VN09</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>/m2 m2 /</t>
+          <t>Escalerilla Cordón 25 mm</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="D363" t="n">
-        <v>1.12</v>
+        <v>0.3</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -12018,29 +12301,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>FLX-027-051</t>
+          <t>FLX-CMP-VN10</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>27,5 cm. TRANSFORMADOR
-SISTEMA MOTOR</t>
+          <t>Escalerilla Cinta 50 mm</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>365</v>
+        <v>1.8</v>
       </c>
       <c r="D364" t="n">
-        <v>273.75</v>
+        <v>1.35</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -12057,19 +12343,19 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>FLX-027-052</t>
+          <t>FLX-CMP-VN11</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Solo Gradúa</t>
+          <t>Soporte Techo / Pared 25 mm (Juego)</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>22.3</v>
+        <v>1.2</v>
       </c>
       <c r="D365" t="n">
-        <v>16.73</v>
+        <v>0.9</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -12081,25 +12367,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>FLX-028-053</t>
+          <t>FLX-CMP-VN12</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>ejido 89 - 127 Aluminio, PVC
-y Madera y Tejido 250</t>
+          <t>Soporte Techo / Pared 50 mm (Juego)</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>0.35</v>
+        <v>2.4</v>
       </c>
       <c r="D366" t="n">
-        <v>0.26</v>
+        <v>1.8</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -12111,24 +12400,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>FLX-028-054</t>
+          <t>FLX-CMP-VN13</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>Motor Somfy para Veneciana 24V / 230V</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>1.6</v>
+        <v>145</v>
       </c>
       <c r="D367" t="n">
-        <v>1.2</v>
+        <v>108.75</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -12140,30 +12433,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G367" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>FLX-028-055</t>
+          <t>FLX-VT-89</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>GANCHO
-Tejido 89 - 12
-y Madera</t>
+          <t>Cortina Vertical 89 mm - Colección Teide / Alcazaba</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>0.59</v>
+        <v>42</v>
       </c>
       <c r="D368" t="n">
-        <v>0.44</v>
+        <v>31.5</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -12171,28 +12466,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>FLX-028-056</t>
+          <t>FLX-VT-127</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Cuero</t>
+          <t>Cortina Vertical 127 mm - Colección Teide / Alcazaba</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>141.85</v>
+        <v>38</v>
       </c>
       <c r="D369" t="n">
-        <v>106.39</v>
+        <v>28.5</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -12200,28 +12499,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr"/>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>FLX-028-057</t>
+          <t>FLX-VT-89M</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Madera</t>
+          <t>Cortina Vertical 89 mm - Colección Mulhacén / Aneto</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>111.8</v>
+        <v>49</v>
       </c>
       <c r="D370" t="n">
-        <v>83.84999999999999</v>
+        <v>36.75</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -12229,28 +12532,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr"/>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>FLX-036-058</t>
+          <t>FLX-VT-127M</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ación del tejido conociendo el ancho de la cortina</t>
+          <t>Cortina Vertical 127 mm - Colección Mulhacén / Aneto</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>0.1</v>
+        <v>44</v>
       </c>
       <c r="D371" t="n">
-        <v>0.08</v>
+        <v>33</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -12258,30 +12565,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>FLX-036-059</t>
+          <t>FLX-VT-MAD</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ECHA O IZQUIERDA
-- DERECHA
-MANDOS: MÍNIMO</t>
+          <t>Cortina Vertical Madera 89 mm</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>0.75</v>
+        <v>111.8</v>
       </c>
       <c r="D372" t="n">
-        <v>0.5600000000000001</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -12289,30 +12598,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>FLX-036-060</t>
+          <t>FLX-VT-CUE</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>T.09
-16,50
-39</t>
+          <t>Cortina Vertical Cuero 89 mm</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>67.3</v>
+        <v>141.85</v>
       </c>
       <c r="D373" t="n">
-        <v>50.47</v>
+        <v>106.39</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -12320,32 +12631,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr"/>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>FLX-041-061</t>
+          <t>FLX-CMP-VT01</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>OS: cm.
-4,2
-ALTO CORTINA LARGO MANDOS
--NEGRO
-Hasta</t>
+          <t>Riel Vertical Aluminio Blanco / Plata</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>1.6</v>
+        <v>17.4</v>
       </c>
       <c r="D374" t="n">
-        <v>1.2</v>
+        <v>13.05</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -12353,25 +12664,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>FLX-042-062</t>
+          <t>FLX-CMP-VT02</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>ACCIONAMIENTO MANUAL Premium
-(Ancho máximo</t>
+          <t>Carro Arrastre Vertical con Gancho</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>2.2</v>
+        <v>0.59</v>
       </c>
       <c r="D375" t="n">
-        <v>1.65</v>
+        <v>0.44</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -12383,30 +12697,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>FLX-042-063</t>
+          <t>FLX-CMP-VT03</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ARADO PARA PULSADOR
-Ancho mínimo a fabricar:
-Hasta</t>
+          <t>Cadena de Distancia Inferior 89 mm</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>2.2</v>
+        <v>0.35</v>
       </c>
       <c r="D376" t="n">
-        <v>1.65</v>
+        <v>0.26</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -12414,30 +12730,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>FLX-042-064</t>
+          <t>FLX-CMP-VT04</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>O MANDO A DISTANCIA
-Ancho mínimo a fabricar:
-Hasta</t>
+          <t>Cadena de Distancia Inferior 127 mm</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>2.2</v>
+        <v>0.45</v>
       </c>
       <c r="D377" t="n">
-        <v>1.65</v>
+        <v>0.34</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -12445,25 +12763,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>FLX-042-065</t>
+          <t>FLX-CMP-VT05</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>1 Ud.
-Ud.</t>
+          <t>Contrapeso Inferior 89 mm</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>74</v>
+        <v>0.76</v>
       </c>
       <c r="D378" t="n">
-        <v>55.5</v>
+        <v>0.57</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -12475,26 +12796,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr"/>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>FLX-045-066</t>
+          <t>FLX-CMP-VT06</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>INACIÓN
-DE. / IZ. Premium Premium DE. Cordón-50
-10</t>
+          <t>Contrapeso Inferior 127 mm</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>14.16</v>
+        <v>0.95</v>
       </c>
       <c r="D379" t="n">
-        <v>10.62</v>
+        <v>0.71</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -12506,28 +12829,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G379" t="inlineStr"/>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>FLX-053-067</t>
+          <t>FLX-CMP-VT07</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>remium Cordón PVC Plisada Cordón-50 Cordón/Varilla</t>
+          <t>Motor para Cortina Vertical 230V con Mando</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>0.98</v>
+        <v>365</v>
       </c>
       <c r="D380" t="n">
-        <v>0.73</v>
+        <v>273.75</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -12535,29 +12862,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr"/>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>FLX-055-068</t>
+          <t>FLX-PLI-01</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>xagonal Plus Cordón Monocomando Monocomando
-5uillo</t>
+          <t>Cortina Plisada Premium PLI.01 - Colección 236</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>2.86</v>
+        <v>58</v>
       </c>
       <c r="D381" t="n">
-        <v>2.15</v>
+        <v>43.5</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -12565,29 +12895,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr"/>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>FLX-057-069</t>
+          <t>FLX-PLI-REV</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>VARILLA SISTEMA MANUAL
-MEDIDA MÁXIMO</t>
+          <t>Cortina Plisada Repliegue Reversible PLI.02</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>1.5</v>
+        <v>68</v>
       </c>
       <c r="D382" t="n">
-        <v>1.12</v>
+        <v>51</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -12595,30 +12928,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G382" t="inlineStr"/>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>FLX-061-070</t>
+          <t>FLX-PLI-ND</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>instalación DENOMINACIÓN
-MINI plisada MINI
-Ihesiva</t>
+          <t>Cortina Plisada Noche y Día PLI.03</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>1.7</v>
+        <v>85</v>
       </c>
       <c r="D383" t="n">
-        <v>1.27</v>
+        <v>63.75</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -12626,29 +12961,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>FLX-063-071</t>
+          <t>FLX-PLI-PLI</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>,9 Clip instalación DENOMINACIÓN
-MINI plisada MINI</t>
+          <t>Cortina Plisada Plano Inclinado / Buhardilla PLI.04</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>0.13</v>
+        <v>74</v>
       </c>
       <c r="D384" t="n">
-        <v>0.1</v>
+        <v>55.5</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -12656,28 +12994,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>FLX-071-072</t>
+          <t>FLX-PLI-MONO</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>al Perfil fijo cristal Cinta adhesiva DENOMINACIÓN</t>
+          <t>Cortina Plisada Plus Monocomando PLI.05</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>0.5</v>
+        <v>79</v>
       </c>
       <c r="D385" t="n">
-        <v>0.38</v>
+        <v>59.25</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -12685,30 +13027,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr"/>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>FLX-073-073</t>
+          <t>FLX-PLI-MINI</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>A CORDÓN ALTO CORTINA LARGO MANDOS
-VER
-ANCHO Hasta</t>
+          <t>Cortina Plisada Mini Cristal Accionamiento Manual</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>1.6</v>
+        <v>49</v>
       </c>
       <c r="D386" t="n">
-        <v>1.2</v>
+        <v>36.75</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -12716,31 +13060,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr"/>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>FLX-073-074</t>
+          <t>FLX-PLI-MINIC</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>fa - PLE.05
-17,55 43,00
-Página 80
-15,50</t>
+          <t>Cortina Plisada Mini Accionamiento Cordón</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D387" t="n">
-        <v>31.5</v>
+        <v>33.75</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -12748,28 +13093,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>FLX-073-075</t>
+          <t>FLX-CMP-PL01</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>SOPORTE</t>
+          <t>Perfil Plisada Mini Cristal Blanco (13,3 x 20 mm)</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>1.53</v>
+        <v>19.15</v>
       </c>
       <c r="D388" t="n">
-        <v>1.15</v>
+        <v>14.36</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -12777,28 +13126,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr"/>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>FLX-075-076</t>
+          <t>FLX-CMP-PL02</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>Perfil Fijo Mini Cristal</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>2.32</v>
+        <v>15.81</v>
       </c>
       <c r="D389" t="n">
-        <v>1.74</v>
+        <v>11.86</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -12806,26 +13159,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr"/>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>FLX-078-077</t>
+          <t>FLX-CMP-PL03</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>ARADO PARA PULSADOR
-Ancho mínimo a fabricar:
-Hasta</t>
+          <t>Soporte Tensor Mini Modelo B</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="D390" t="n">
-        <v>1.65</v>
+        <v>0.38</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -12837,26 +13192,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>FLX-078-078</t>
+          <t>FLX-CMP-PL04</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>O MANDO A DISTANCIA
-Ancho mínimo a fabricar:
-Hasta</t>
+          <t>Freno Cordón Plisada Mini</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="D391" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -12868,24 +13225,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>FLX-089-079</t>
+          <t>FLX-CMP-PL05</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Varilla Mando</t>
+          <t>Cordoncillo Plisada 1,2 mm</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>1.5</v>
+        <v>0.63</v>
       </c>
       <c r="D392" t="n">
-        <v>1.12</v>
+        <v>0.47</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -12897,28 +13258,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>FLX-091-080</t>
+          <t>FLX-PLE-01</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Cinta</t>
+          <t>Cortina Plegable Confeccionada Sistema Plus PLE.01</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>4.75</v>
+        <v>55</v>
       </c>
       <c r="D393" t="n">
-        <v>3.56</v>
+        <v>41.25</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -12926,31 +13291,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>FLX-092-081</t>
+          <t>FLX-PLE-LON</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>X
-PL. 4153
-(Poliéster)
-PL. 4155 Colores especiales</t>
+          <t>Cortina Plegable La Loneta PLE.05</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>5.7</v>
+        <v>62</v>
       </c>
       <c r="D394" t="n">
-        <v>4.28</v>
+        <v>46.5</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -12958,31 +13324,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>FLX-092-082</t>
+          <t>FLX-PLE-VIS</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>16,00
-28,00
-ÑO
-25,00</t>
+          <t>Cortina Plegable El Visillo PLE.06</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D395" t="n">
-        <v>15</v>
+        <v>43.5</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -12990,26 +13357,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>FLX-096-083</t>
+          <t>FLX-CMP-PLE01</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>CORTINA COMPLETA
-S
-TARIFA</t>
+          <t>Mecanismo Plegable a Cadena con Reductor</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>63</v>
+        <v>22.5</v>
       </c>
       <c r="D396" t="n">
-        <v>47.25</v>
+        <v>16.88</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
@@ -13021,29 +13390,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr"/>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>FLX-096-084</t>
+          <t>FLX-CMP-PLE02</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>CORTADO
-AL ANCHO</t>
+          <t>Perfil Velcrado Plegable Plus</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>27.05</v>
+        <v>10.92</v>
       </c>
       <c r="D397" t="n">
-        <v>20.29</v>
+        <v>8.19</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -13051,35 +13423,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>FLX-096-085</t>
+          <t>FLX-CMP-PLE03</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>24,60
-22,20
-13,45
-24,80
-28,45
-21,90
-16,25
-29,20</t>
+          <t>Pletina Inferior Aluminio Plegable 40 mm</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>28.35</v>
+        <v>3.55</v>
       </c>
       <c r="D398" t="n">
-        <v>21.26</v>
+        <v>2.66</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -13087,32 +13456,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>FLX-096-086</t>
+          <t>FLX-CMP-PLE04</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>27,30
-20,45
-37,95
-35,20
-33,75</t>
+          <t>Varilla Fibra de Vidrio Plegable 4 mm</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>43.65</v>
+        <v>0.6</v>
       </c>
       <c r="D399" t="n">
-        <v>32.74</v>
+        <v>0.45</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -13120,35 +13489,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>FLX-096-087</t>
+          <t>FLX-PAN-2V</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>35,20
-55,10
-55,10
-33,05
-28,35
-45,00
-57,10
-45,00</t>
+          <t>Panel Deslizante / Japonés 2 Vías Sistema Básico</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>57.1</v>
+        <v>48</v>
       </c>
       <c r="D400" t="n">
-        <v>42.83</v>
+        <v>36</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -13156,28 +13522,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>FLX-096-088</t>
+          <t>FLX-PAN-3V</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>67,20</t>
+          <t>Panel Deslizante / Japonés 3 Vías Sistema Básico</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>29.9</v>
+        <v>65</v>
       </c>
       <c r="D401" t="n">
-        <v>22.42</v>
+        <v>48.75</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -13185,28 +13555,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>FLX-096-089</t>
+          <t>FLX-PAN-4V</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>41,05</t>
+          <t>Panel Deslizante / Japonés 4 Vías Sistema Básico</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>29.3</v>
+        <v>82</v>
       </c>
       <c r="D402" t="n">
-        <v>21.98</v>
+        <v>61.5</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -13214,31 +13588,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>FLX-096-090</t>
+          <t>FLX-PAN-5V</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>43,65
-35,20
-55,20
-29,90</t>
+          <t>Panel Deslizante / Japonés 5 Vías Sistema Básico</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>37.95</v>
+        <v>98</v>
       </c>
       <c r="D403" t="n">
-        <v>28.46</v>
+        <v>73.5</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -13246,26 +13621,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>FLX-096-091</t>
+          <t>FLX-PAN-MOT</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>28,35 35,20 270
-14,10 18,55 300
-24,80 31,10 300</t>
+          <t>Panel Deslizante Sistema Motor 3 a 5 Vías</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>23.75</v>
+        <v>280</v>
       </c>
       <c r="D404" t="n">
-        <v>17.81</v>
+        <v>210</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -13277,30 +13654,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>FLX-097-092</t>
+          <t>FLX-CMP-PAN01</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>43 CON
-ACCIONAMIENTO A CADENA
-SIN REDUCTOR</t>
+          <t>Portatela Velcrado Deslizante</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>120</v>
+        <v>19.77</v>
       </c>
       <c r="D405" t="n">
-        <v>90</v>
+        <v>14.83</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -13308,24 +13687,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>FLX-097-093</t>
+          <t>FLX-CMP-PAN02</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>4,5 X 6</t>
+          <t>Trineo Arrastre Panel Deslizante</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>6.5</v>
+        <v>7.51</v>
       </c>
       <c r="D406" t="n">
-        <v>4.88</v>
+        <v>5.63</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -13337,24 +13720,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>FLX-097-094</t>
+          <t>FLX-CMP-PAN03</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>ÓPICO</t>
+          <t>Varilla de Mando Tirador 1,50 m</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>23.4</v>
+        <v>3.38</v>
       </c>
       <c r="D407" t="n">
-        <v>17.55</v>
+        <v>2.54</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -13366,29 +13753,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>FLX-097-095</t>
+          <t>FLX-ENR-UNI</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>PERFIL ADHESIVO 37,24
-TORNILLO 4 x 4 0,48</t>
+          <t>Cortina Enrollable Universal EN.0 (Sin Tejido)</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D408" t="n">
-        <v>29.25</v>
+        <v>21</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>ml.</t>
+          <t>ud.</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -13396,28 +13786,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>FLX-099-096</t>
+          <t>FLX-ENR-SAT</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>Cortina Enrollable Screen Satiné 5500</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>1.61</v>
+        <v>63</v>
       </c>
       <c r="D409" t="n">
-        <v>1.21</v>
+        <v>47.25</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -13425,29 +13819,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>FLX-099-097</t>
+          <t>FLX-ENR-KAR</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>1,12
-7,92</t>
+          <t>Cortina Enrollable Screen Karellis 11301</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>8.44</v>
+        <v>68</v>
       </c>
       <c r="D410" t="n">
-        <v>6.33</v>
+        <v>51</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -13455,29 +13852,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>FLX-100-098</t>
+          <t>FLX-ENR-OPA</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>SIN ZIP CON
-AL</t>
+          <t>Cortina Enrollable Tejido Opaco Vela</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D411" t="n">
-        <v>55.5</v>
+        <v>40.5</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -13485,28 +13885,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>FLX-100-099</t>
+          <t>FLX-ENR-BAL</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>MANIVELA</t>
+          <t>Cortina Enrollable Tejido Bali / Madeira EN.06</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>60.5</v>
+        <v>72</v>
       </c>
       <c r="D412" t="n">
-        <v>45.38</v>
+        <v>54</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -13514,29 +13918,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>FLX-101-100</t>
+          <t>FLX-ENR-CAJ42</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>BLANCO
-MANIVELA</t>
+          <t>Cortina Enrollable con Cajón de 42 mm</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>1.5</v>
+        <v>72</v>
       </c>
       <c r="D413" t="n">
-        <v>1.12</v>
+        <v>54</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -13544,33 +13951,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>FLX-104-101</t>
+          <t>FLX-ENR-CAJ90</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Ud.
-3,55
-10,00
-10,00
-8,96
-11,60</t>
+          <t>Cortina Enrollable con Cajón de 90 mm CA.04</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="D414" t="n">
-        <v>3</v>
+        <v>73.5</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -13578,33 +13984,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>FLX-118-102</t>
+          <t>FLX-ENR-ZIP</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>A CABLE PARA MOTOR
-A G
-F
-8,4 cm.
-cm.
-ESCUADRA DE 8</t>
+          <t>Cortina Enrollable Sistema ZIP Guiada</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>3.26</v>
+        <v>135</v>
       </c>
       <c r="D415" t="n">
-        <v>2.44</v>
+        <v>101.25</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -13621,24 +14026,23 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>FLX-121-103</t>
+          <t>FLX-ENR-CAB</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>/Ud.- m.
-Alto cortina</t>
+          <t>Cortina Enrollable Guiada a Cable de Acero</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>2.13</v>
+        <v>78</v>
       </c>
       <c r="D416" t="n">
-        <v>1.6</v>
+        <v>58.5</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -13646,30 +14050,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>FLX-121-104</t>
+          <t>FLX-ENR-BUH</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>1,3 cm.
-cm.
-5,5</t>
+          <t>Cortina Enrollable Buhardilla con Guías Laterales</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>2.25</v>
+        <v>85</v>
       </c>
       <c r="D417" t="n">
-        <v>1.69</v>
+        <v>63.75</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -13677,29 +14083,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>FLX-121-105</t>
+          <t>FLX-LM-01</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>cm.
-6</t>
+          <t>Cortina Luz Mágica LM.01 Alborada Galería 80</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>2.8</v>
+        <v>88</v>
       </c>
       <c r="D418" t="n">
-        <v>2.1</v>
+        <v>66</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -13707,30 +14116,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>FLX-122-106</t>
+          <t>FLX-LM-03</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>toe DENOMINACIÓN
-D D.58 0 0 to R
-D-43 R-1:1,159,76</t>
+          <t>Cortina Luz Mágica LM.03 Niebla Galería 90</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>15.49</v>
+        <v>96</v>
       </c>
       <c r="D419" t="n">
-        <v>11.62</v>
+        <v>72</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -13738,28 +14149,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G419" t="inlineStr"/>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>FLX-122-107</t>
+          <t>FLX-CMP-EN01</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>0,48 15,68 0,55</t>
+          <t>Eje Aluminio D.43 mm para Enrollable</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>2.08</v>
+        <v>9.76</v>
       </c>
       <c r="D420" t="n">
-        <v>1.56</v>
+        <v>7.32</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -13767,30 +14182,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>FLX-122-108</t>
+          <t>FLX-CMP-EN02</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>D-43 R-1:1,159,76
-D-43 R-1:3 19,06
-D-58 R-1:4</t>
+          <t>Eje Aluminio D.58 mm para Enrollable</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>39.26</v>
+        <v>19.92</v>
       </c>
       <c r="D421" t="n">
-        <v>29.45</v>
+        <v>14.94</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -13798,28 +14215,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>FLX-122-109</t>
+          <t>FLX-CMP-EN03</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>4,5X6 0,82 3,55 Cerrada 1,00 4,45 Cerrada 1,50</t>
+          <t>Eje Aluminio D.80 mm para Enrollable</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>5.34</v>
+        <v>34.52</v>
       </c>
       <c r="D422" t="n">
-        <v>4</v>
+        <v>25.89</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -13827,26 +14248,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr"/>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>FLX-122-110</t>
+          <t>FLX-CMP-EN04</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>d Ma up eta lld eor DENOMINACIÓN
-R to M to 0cho
-9e</t>
+          <t>Mecanismo Cadena D.43 Desmultiplicado 1:3</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>28.44</v>
+        <v>19.06</v>
       </c>
       <c r="D423" t="n">
-        <v>21.33</v>
+        <v>14.29</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
@@ -13858,24 +14281,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G423" t="inlineStr"/>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>FLX-122-111</t>
+          <t>FLX-CMP-EN05</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>0,97 21,30 24,66</t>
+          <t>Mecanismo Cadena D.58 Desmultiplicado 1:4</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>2.08</v>
+        <v>39.26</v>
       </c>
       <c r="D424" t="n">
-        <v>1.56</v>
+        <v>29.45</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
@@ -13887,24 +14314,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G424" t="inlineStr"/>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>FLX-127-112</t>
+          <t>FLX-CMP-EN06</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>f j oi ól nC R i 1e e1r c0r te o DENOMINACIÓN E je</t>
+          <t>Cadena Mando PVC 4,5 x 6 mm Cerrada 1,50 m</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>34.52</v>
+        <v>4.45</v>
       </c>
       <c r="D425" t="n">
-        <v>25.89</v>
+        <v>3.34</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
@@ -13916,24 +14347,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr"/>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>FLX-127-113</t>
+          <t>FLX-CMP-EN07</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>9,13 19,72 0,97</t>
+          <t>Cadena Mando PVC 4,5 x 6 mm Cerrada 2,00 m</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>5.36</v>
+        <v>5.34</v>
       </c>
       <c r="D426" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
@@ -13945,28 +14380,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr"/>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>FLX-127-114</t>
+          <t>FLX-CMP-EN08</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>4,5X6 0,82 3,55 Cerrada 1,00 4,45 Cerrada 1,50</t>
+          <t>Cadena Mando Metálica Continua</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>5.34</v>
+        <v>6.5</v>
       </c>
       <c r="D427" t="n">
-        <v>4</v>
+        <v>4.88</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -13974,27 +14413,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr"/>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>FLX-127-115</t>
+          <t>FLX-CMP-EN09</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>/125
-. .78 0 R o o to
-110
-48,75 34,52 42,33 55,58</t>
+          <t>Soportes Pared / Techo Enrollable 40 mm (Juego)</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>9.640000000000001</v>
+        <v>5</v>
       </c>
       <c r="D428" t="n">
-        <v>7.23</v>
+        <v>3.75</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
@@ -14006,24 +14446,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr"/>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>FLX-127-116</t>
+          <t>FLX-CMP-EN10</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>26,2878,80 2,08</t>
+          <t>Soportes Pared / Techo Enrollable 60 mm (Juego)</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>0.97</v>
+        <v>7.31</v>
       </c>
       <c r="D429" t="n">
-        <v>0.73</v>
+        <v>5.48</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
@@ -14035,24 +14479,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G429" t="inlineStr"/>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>FLX-132-117</t>
+          <t>FLX-CMP-EN11</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>vf j oi ól nC R 1ie e2r c5r te o DENOMINACIÓN E je</t>
+          <t>Soportes Pared / Techo Enrollable 75 mm (Juego)</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>34.52</v>
+        <v>14.49</v>
       </c>
       <c r="D430" t="n">
-        <v>25.89</v>
+        <v>10.87</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
@@ -14064,28 +14512,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G430" t="inlineStr"/>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>FLX-132-118</t>
+          <t>FLX-CMP-EN12</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>9,13 0,97 5,36</t>
+          <t>Cajón de Aluminio 90 mm Curvo / Recto</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>19.72</v>
+        <v>33.51</v>
       </c>
       <c r="D431" t="n">
-        <v>14.79</v>
+        <v>25.13</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -14093,28 +14545,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G431" t="inlineStr"/>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>FLX-132-119</t>
+          <t>FLX-CMP-EN13</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>4,5X6 0,82 3,55 Cerrada 1,00 4,45 Cerrada 1,50</t>
+          <t>Guía ZIP 50 x 34 mm con Clip</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>5.34</v>
+        <v>22.6</v>
       </c>
       <c r="D432" t="n">
-        <v>4</v>
+        <v>16.95</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -14122,29 +14578,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G432" t="inlineStr"/>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>FLX-132-120</t>
+          <t>FLX-CMP-EN14</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>70 78 (Juego) 110/125 Curvo Recto Curvo Recto
-125</t>
+          <t>Guía Ventilada Blanca con Pistón</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>48.75</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="D433" t="n">
-        <v>36.56</v>
+        <v>6.48</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -14152,31 +14611,32 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G433" t="inlineStr"/>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>FLX-132-121</t>
+          <t>FLX-CMP-EN15</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>78
-5,91 7,69
-Corona
-6,03</t>
+          <t>Guía Cerrada 55 mm Instalación en Hueco / Frontal</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>3.57</v>
+        <v>19.92</v>
       </c>
       <c r="D434" t="n">
-        <v>2.68</v>
+        <v>14.94</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>ud.</t>
+          <t>ml.</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -14184,24 +14644,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G434" t="inlineStr"/>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>FLX-132-122</t>
+          <t>FLX-CMP-EN16</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>26,2878,80 2,08</t>
+          <t>Accionamiento a Manivela Máquina 1:8 con Manivela 1,50 m</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>0.97</v>
+        <v>205</v>
       </c>
       <c r="D435" t="n">
-        <v>0.73</v>
+        <v>153.75</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
@@ -14213,26 +14677,28 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr"/>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>FLX-140-123</t>
+          <t>FLX-CMP-EN17</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Tornillo 2,9x9,5 DENOMINACIÓN
-DS DS DS DS
-25,23</t>
+          <t>Motorización Somfy para Enrollable D.40 / D.50</t>
         </is>
       </c>
       <c r="C436" t="n">
-        <v>0.05</v>
+        <v>165</v>
       </c>
       <c r="D436" t="n">
-        <v>0.04</v>
+        <v>123.75</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
@@ -14244,187 +14710,11 @@
           <t>Flexol</t>
         </is>
       </c>
-      <c r="G436" t="inlineStr"/>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>FLX-140-124</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>Cadena
-Pequeño Mediano Grande Medio Fuerte SIM SIM</t>
-        </is>
-      </c>
-      <c r="C437" t="n">
-        <v>74.03</v>
-      </c>
-      <c r="D437" t="n">
-        <v>55.52</v>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G437" t="inlineStr"/>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>FLX-142-125</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>X PL. 4153
-(Poliéster)
-PL. 4155
-Colores especiales</t>
-        </is>
-      </c>
-      <c r="C438" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="D438" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G438" t="inlineStr"/>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>FLX-150-126</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>RADIO
-AM35 PLUS L 6/18 D.43/58 6 18 14,8 36 W. 40</t>
-        </is>
-      </c>
-      <c r="C439" t="n">
-        <v>329</v>
-      </c>
-      <c r="D439" t="n">
-        <v>246.75</v>
-      </c>
-      <c r="E439" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F439" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G439" t="inlineStr"/>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>FLX-151-127</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>Blanco: 38,16 Plata:</t>
-        </is>
-      </c>
-      <c r="C440" t="n">
-        <v>39.94</v>
-      </c>
-      <c r="D440" t="n">
-        <v>29.95</v>
-      </c>
-      <c r="E440" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G440" t="inlineStr"/>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>FLX-151-128</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>Blanco: 33,97 Plata:</t>
-        </is>
-      </c>
-      <c r="C441" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="D441" t="n">
-        <v>26.78</v>
-      </c>
-      <c r="E441" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G441" t="inlineStr"/>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>FLX-151-129</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>Blanco:11,76
-Plata:</t>
-        </is>
-      </c>
-      <c r="C442" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="D442" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G442" t="inlineStr"/>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>extracted_images/motor_p1_600500001.png</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/precios_catalogo.xlsx
+++ b/precios_catalogo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G436"/>
+  <dimension ref="A1:G265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9073,5649 +9073,6 @@
       </c>
       <c r="G265" t="inlineStr"/>
     </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>MQ-ENR-01</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Mosquitera Enrollable Ventana 42 - Grupo 1 (Blanco)</t>
-        </is>
-      </c>
-      <c r="C266" t="n">
-        <v>48</v>
-      </c>
-      <c r="D266" t="n">
-        <v>36</v>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>MQ-ENR-02</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Mosquitera Enrollable Ventana 42 - Grupo 2 (Plata / Bronce / RAL Estándar)</t>
-        </is>
-      </c>
-      <c r="C267" t="n">
-        <v>54</v>
-      </c>
-      <c r="D267" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>MQ-ENR-03</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Mosquitera Enrollable Ventana 42 - Grupo 3 (Madera / Foliado)</t>
-        </is>
-      </c>
-      <c r="C268" t="n">
-        <v>62</v>
-      </c>
-      <c r="D268" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>MQ-ENR-MUE</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Muelle de retención para Mosquitera Enrollable 42</t>
-        </is>
-      </c>
-      <c r="C269" t="n">
-        <v>12</v>
-      </c>
-      <c r="D269" t="n">
-        <v>9</v>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>MQ-ENR-AV1</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Guías con 1 Felpudo Antiviento (Incremento)</t>
-        </is>
-      </c>
-      <c r="C270" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D270" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>MQ-ENR-AV2</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Guías con 2 Felpudos Antiviento (Incremento)</t>
-        </is>
-      </c>
-      <c r="C271" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="D271" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>MQ-ENR-DAV1</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Guía doble con 1 Felpudo Antiviento (Incremento)</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D272" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>MQ-ENR-DAV2</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Guía doble con 2 Felpudos Antiviento (Incremento)</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="D273" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>MQ-ENR-TET20</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Malla TETUG 20-1400 enrollada en eje</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="D274" t="n">
-        <v>21.38</v>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>MQ-ENR-TET25</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Malla TETUG 25-1400 enrollada en eje</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="D275" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>MQ-ENR-TET23</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Malla TETUG 23-1400 Enrollable Puerta</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>37.12</v>
-      </c>
-      <c r="D276" t="n">
-        <v>27.84</v>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>MQ-ENR-PTA1</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Mosquitera Enrollable Puerta Lateral Única - Grupo 1</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>125</v>
-      </c>
-      <c r="D277" t="n">
-        <v>93.75</v>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>MQ-ENR-PTA2</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Mosquitera Enrollable Puerta Lateral Doble - Grupo 1</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>230</v>
-      </c>
-      <c r="D278" t="n">
-        <v>172.5</v>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PTA01</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Perfil Cierre Imán Enrollable Puerta</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>11.47</v>
-      </c>
-      <c r="D279" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PTA02</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Eslabón Antiviento Enrollable Puerta (Juego)</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="D280" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PTA03</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Cadena Inferior Enrollable Puerta</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>49.08</v>
-      </c>
-      <c r="D281" t="n">
-        <v>36.81</v>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PTA04</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Imán Perfil Móvil Enrollable Puerta</t>
-        </is>
-      </c>
-      <c r="C282" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D282" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PTA05</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Imán Perfil Cierre Enrollable Puerta</t>
-        </is>
-      </c>
-      <c r="C283" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="D283" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PTA06</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Portaimán Enrollable Puerta</t>
-        </is>
-      </c>
-      <c r="C284" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="D284" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PTA07</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>Hilo Trenzado Negro Enrollable Puerta</t>
-        </is>
-      </c>
-      <c r="C285" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="D285" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PTA08</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>Carril Inferior Enrollable Puerta</t>
-        </is>
-      </c>
-      <c r="C286" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="D286" t="n">
-        <v>10.93</v>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PTA09</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Perfil Móvil Enrollable Puerta (G1 Blanco)</t>
-        </is>
-      </c>
-      <c r="C287" t="n">
-        <v>38.18</v>
-      </c>
-      <c r="D287" t="n">
-        <v>28.63</v>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PTA10</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>Carril Superior Enrollable Puerta (G1 Blanco)</t>
-        </is>
-      </c>
-      <c r="C288" t="n">
-        <v>28.84</v>
-      </c>
-      <c r="D288" t="n">
-        <v>21.63</v>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PTA11</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Perfil Fijo Enrollable Puerta (G1 Blanco)</t>
-        </is>
-      </c>
-      <c r="C289" t="n">
-        <v>31.97</v>
-      </c>
-      <c r="D289" t="n">
-        <v>23.98</v>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PTA12</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Fleje Enrollable Puerta</t>
-        </is>
-      </c>
-      <c r="C290" t="n">
-        <v>7</v>
-      </c>
-      <c r="D290" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PTA13</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>Kit Felpudo 4,8 x 19 mm Enrollable Puerta</t>
-        </is>
-      </c>
-      <c r="C291" t="n">
-        <v>85.88</v>
-      </c>
-      <c r="D291" t="n">
-        <v>64.41</v>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>MQ-PLI-22-1</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>Mosquitera Plisada 22 Puerta Única - Grupo 1</t>
-        </is>
-      </c>
-      <c r="C292" t="n">
-        <v>135</v>
-      </c>
-      <c r="D292" t="n">
-        <v>101.25</v>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>MQ-PLI-22-2</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Mosquitera Plisada 22 Puerta Doble - Grupo 1</t>
-        </is>
-      </c>
-      <c r="C293" t="n">
-        <v>245</v>
-      </c>
-      <c r="D293" t="n">
-        <v>183.75</v>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>MQ-PLI-22-REV</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Mosquitera Plisada 22 Reversible - Grupo 1</t>
-        </is>
-      </c>
-      <c r="C294" t="n">
-        <v>155</v>
-      </c>
-      <c r="D294" t="n">
-        <v>116.25</v>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>MQ-PLI-22-VEN</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Mosquitera Plisada 22 Ventana - Grupo 1</t>
-        </is>
-      </c>
-      <c r="C295" t="n">
-        <v>85</v>
-      </c>
-      <c r="D295" t="n">
-        <v>63.75</v>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL22-01</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Perfil Fijo Plisada 22 (G1 Blanco)</t>
-        </is>
-      </c>
-      <c r="C296" t="n">
-        <v>12.37</v>
-      </c>
-      <c r="D296" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL22-02</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Carril Superior Plisada 22 (G1 Blanco)</t>
-        </is>
-      </c>
-      <c r="C297" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="D297" t="n">
-        <v>10.23</v>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL22-03</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Perfil Móvil Plisada 22 (G1 Blanco)</t>
-        </is>
-      </c>
-      <c r="C298" t="n">
-        <v>21.98</v>
-      </c>
-      <c r="D298" t="n">
-        <v>16.48</v>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL22-04</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Carril Inferior Aluminio Negro Plisada 22</t>
-        </is>
-      </c>
-      <c r="C299" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="D299" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL22-05</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Adhesivo Carril Inferior Plisada 22</t>
-        </is>
-      </c>
-      <c r="C300" t="n">
-        <v>2</v>
-      </c>
-      <c r="D300" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL22-06</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Clip Hilo Plisada 22 / 40</t>
-        </is>
-      </c>
-      <c r="C301" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="D301" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL22-07</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Hilo Negro Plisada 22 / 40</t>
-        </is>
-      </c>
-      <c r="C302" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="D302" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL22-08</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>Imán Perfil Fijo Plisada 22</t>
-        </is>
-      </c>
-      <c r="C303" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="D303" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL22-09</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>Imán Perfil Móvil Plisada 22</t>
-        </is>
-      </c>
-      <c r="C304" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D304" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL22-10</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Malla Plisada 22 - 2400 mm</t>
-        </is>
-      </c>
-      <c r="C305" t="n">
-        <v>50.64</v>
-      </c>
-      <c r="D305" t="n">
-        <v>37.98</v>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL22-11</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Malla Plisada 22 - 3000 mm</t>
-        </is>
-      </c>
-      <c r="C306" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="D306" t="n">
-        <v>58.05</v>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL22-12</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Lámina Fijación Malla 22</t>
-        </is>
-      </c>
-      <c r="C307" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="D307" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL22-13</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Perfil Instalación Frontal Plisada 22 (G1 Blanco)</t>
-        </is>
-      </c>
-      <c r="C308" t="n">
-        <v>22.95</v>
-      </c>
-      <c r="D308" t="n">
-        <v>17.21</v>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>MQ-PLI-40-1</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Mosquitera Plisada 40 Puerta Única - Grupo 1</t>
-        </is>
-      </c>
-      <c r="C309" t="n">
-        <v>326</v>
-      </c>
-      <c r="D309" t="n">
-        <v>244.5</v>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>MQ-PLI-40-2</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>Mosquitera Plisada 40 Puerta Doble - Grupo 1</t>
-        </is>
-      </c>
-      <c r="C310" t="n">
-        <v>653</v>
-      </c>
-      <c r="D310" t="n">
-        <v>489.75</v>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-01</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>Perfil Fijo Plisada 40 (G1 Blanco)</t>
-        </is>
-      </c>
-      <c r="C311" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="D311" t="n">
-        <v>17.92</v>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-02</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Perfil Móvil Plisada 40 (G1 Blanco)</t>
-        </is>
-      </c>
-      <c r="C312" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="D312" t="n">
-        <v>18.67</v>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-03</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Carril Superior Plisada 40 (G1 Blanco)</t>
-        </is>
-      </c>
-      <c r="C313" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="D313" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-04</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Perfil Cierre Imán Plisada 40</t>
-        </is>
-      </c>
-      <c r="C314" t="n">
-        <v>11.93</v>
-      </c>
-      <c r="D314" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-05</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Porta Imán Plisada 40</t>
-        </is>
-      </c>
-      <c r="C315" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="D315" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-06</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Carril Inferior Gris Adhesivo Plisada 40</t>
-        </is>
-      </c>
-      <c r="C316" t="n">
-        <v>29.28</v>
-      </c>
-      <c r="D316" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-07</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Cadena 58 Eslabones Plisada 40</t>
-        </is>
-      </c>
-      <c r="C317" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="D317" t="n">
-        <v>36.45</v>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-08</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Cadena 3 Eslabones Plisada 40</t>
-        </is>
-      </c>
-      <c r="C318" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D318" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-09</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>Eslabón Reversible Plisada 40</t>
-        </is>
-      </c>
-      <c r="C319" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D319" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-10</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>Eslabón Gancho Plisada 40</t>
-        </is>
-      </c>
-      <c r="C320" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="D320" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-11</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Eslabón Rojo Plisada 40</t>
-        </is>
-      </c>
-      <c r="C321" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="D321" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-12</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Eslabón Blanco Plisada 40</t>
-        </is>
-      </c>
-      <c r="C322" t="n">
-        <v>2</v>
-      </c>
-      <c r="D322" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-13</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Maneta Plisada 40</t>
-        </is>
-      </c>
-      <c r="C323" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D323" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-14</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Malla Plisada 40 - 2200 mm</t>
-        </is>
-      </c>
-      <c r="C324" t="n">
-        <v>56.04</v>
-      </c>
-      <c r="D324" t="n">
-        <v>42.03</v>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-15</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Malla Plisada 40 - 2600 mm</t>
-        </is>
-      </c>
-      <c r="C325" t="n">
-        <v>62.56</v>
-      </c>
-      <c r="D325" t="n">
-        <v>46.92</v>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-16</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Cantonera Superior P. Móvil 40</t>
-        </is>
-      </c>
-      <c r="C326" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="D326" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-17</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Cantonera Superior P. Fijo 40</t>
-        </is>
-      </c>
-      <c r="C327" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="D327" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-18</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Cantonera Inferior P. Móvil 40</t>
-        </is>
-      </c>
-      <c r="C328" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="D328" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>MQ-CMP-PL40-19</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Cantonera Inferior P. Fijo 40</t>
-        </is>
-      </c>
-      <c r="C329" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="D329" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>MQ-ABA-1</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Mosquitera Abatible Puerta 1 Hoja - Grupo 1 (Blanco)</t>
-        </is>
-      </c>
-      <c r="C330" t="n">
-        <v>303</v>
-      </c>
-      <c r="D330" t="n">
-        <v>227.25</v>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>MQ-ABA-2</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Mosquitera Abatible Puerta 2 Hojas - Grupo 1 (Blanco)</t>
-        </is>
-      </c>
-      <c r="C331" t="n">
-        <v>605</v>
-      </c>
-      <c r="D331" t="n">
-        <v>453.75</v>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>MQ-CMP-AB01</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Perfil Marco Abatible (G1 Blanco)</t>
-        </is>
-      </c>
-      <c r="C332" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="D332" t="n">
-        <v>13.88</v>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>MQ-CMP-AB02</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Perfil Hoja Abatible (G1 Blanco)</t>
-        </is>
-      </c>
-      <c r="C333" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="D333" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>MQ-CMP-AB03</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Perfil Encuentro Abatible 2 Hojas (G1 Blanco)</t>
-        </is>
-      </c>
-      <c r="C334" t="n">
-        <v>13.27</v>
-      </c>
-      <c r="D334" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>MQ-CMP-AB04</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Perfil Travesaño Abatible (G1 Blanco)</t>
-        </is>
-      </c>
-      <c r="C335" t="n">
-        <v>10.93</v>
-      </c>
-      <c r="D335" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>MQ-CMP-AB05</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Bisagra con Muelle de Retorno Abatible</t>
-        </is>
-      </c>
-      <c r="C336" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="D336" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>MQ-FIJ-1</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Mosquitera Fija con Marco - Grupo 1 (Blanco)</t>
-        </is>
-      </c>
-      <c r="C337" t="n">
-        <v>38</v>
-      </c>
-      <c r="D337" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>MQ-FIJ-2</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Mosquitera Fija con Marco - Grupo 2 (Plata / RAL)</t>
-        </is>
-      </c>
-      <c r="C338" t="n">
-        <v>44</v>
-      </c>
-      <c r="D338" t="n">
-        <v>33</v>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>MQ-COR-1</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Mosquitera Corredera Perfil Curvo - Grupo 1 (Blanco)</t>
-        </is>
-      </c>
-      <c r="C339" t="n">
-        <v>45</v>
-      </c>
-      <c r="D339" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>MQ-COR-2</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Mosquitera Corredera Perfil Curvo - Grupo 2 (Plata / RAL)</t>
-        </is>
-      </c>
-      <c r="C340" t="n">
-        <v>52</v>
-      </c>
-      <c r="D340" t="n">
-        <v>39</v>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>MQ-CMP-CR01</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Marco Corredera Guía Z - Grupo 1 (Blanco)</t>
-        </is>
-      </c>
-      <c r="C341" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="D341" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>MQ-CMP-CR02</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Rodamientos Rueda Corredera (Juego)</t>
-        </is>
-      </c>
-      <c r="C342" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="D342" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>MQ-INC-TRAV</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Travesaño Adicional Mosquitera (Incremento)</t>
-        </is>
-      </c>
-      <c r="C343" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="D343" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>MQ-INC-IRR</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Forma Irregular / Plantilla (Incremento)</t>
-        </is>
-      </c>
-      <c r="C344" t="n">
-        <v>27</v>
-      </c>
-      <c r="D344" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>MQ-INC-MEDP</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Medio Punto / Arco Curva Monoradio (Incremento)</t>
-        </is>
-      </c>
-      <c r="C345" t="n">
-        <v>100</v>
-      </c>
-      <c r="D345" t="n">
-        <v>75</v>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>MQ-INC-BUEY</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Ojo de Buey / Curva Multiradio (Incremento)</t>
-        </is>
-      </c>
-      <c r="C346" t="n">
-        <v>250</v>
-      </c>
-      <c r="D346" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>MQ-EXP-01</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Carta de Colores Mosquiflex</t>
-        </is>
-      </c>
-      <c r="C347" t="n">
-        <v>10</v>
-      </c>
-      <c r="D347" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>MQ-EXP-02</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Expositor Personalizable Mosquiflex</t>
-        </is>
-      </c>
-      <c r="C348" t="n">
-        <v>590</v>
-      </c>
-      <c r="D348" t="n">
-        <v>442.5</v>
-      </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>Mosquiflex</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>FLX-VEN-16</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Veneciana Aluminio 16 mm - Colores Básicos</t>
-        </is>
-      </c>
-      <c r="C349" t="n">
-        <v>35</v>
-      </c>
-      <c r="D349" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>FLX-VEN-25</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Veneciana Aluminio 25 mm - Colores Básicos</t>
-        </is>
-      </c>
-      <c r="C350" t="n">
-        <v>29</v>
-      </c>
-      <c r="D350" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>FLX-VEN-50</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Veneciana Aluminio 50 mm - Colores Básicos con Cordón</t>
-        </is>
-      </c>
-      <c r="C351" t="n">
-        <v>42</v>
-      </c>
-      <c r="D351" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>FLX-VEN-50C</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>Veneciana Aluminio 50 mm - Colores Básicos con Cinta</t>
-        </is>
-      </c>
-      <c r="C352" t="n">
-        <v>48</v>
-      </c>
-      <c r="D352" t="n">
-        <v>36</v>
-      </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>FLX-VEN-MAD</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Veneciana Madera 50 mm - Colección Madeira / Bali</t>
-        </is>
-      </c>
-      <c r="C353" t="n">
-        <v>78</v>
-      </c>
-      <c r="D353" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>FLX-VEN-MAD2</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Veneciana Madera 50 mm - Colección Ceylan / Seychelles</t>
-        </is>
-      </c>
-      <c r="C354" t="n">
-        <v>88</v>
-      </c>
-      <c r="D354" t="n">
-        <v>66</v>
-      </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VN01</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>Cabezal de Aluminio 25 mm</t>
-        </is>
-      </c>
-      <c r="C355" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="D355" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VN02</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Cabezal de Aluminio 50 mm</t>
-        </is>
-      </c>
-      <c r="C356" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="D356" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VN03</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Terminal Inferior Aluminio 25 mm</t>
-        </is>
-      </c>
-      <c r="C357" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="D357" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VN04</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Terminal Inferior Aluminio 50 mm</t>
-        </is>
-      </c>
-      <c r="C358" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="D358" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VN05</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Galería Madera G-1 para incrustar en hueco</t>
-        </is>
-      </c>
-      <c r="C359" t="n">
-        <v>15.51</v>
-      </c>
-      <c r="D359" t="n">
-        <v>11.63</v>
-      </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VN06</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>Galería Madera G-3 en U</t>
-        </is>
-      </c>
-      <c r="C360" t="n">
-        <v>29.42</v>
-      </c>
-      <c r="D360" t="n">
-        <v>22.07</v>
-      </c>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VN07</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>Maquinilla Freno Cordón 25 mm</t>
-        </is>
-      </c>
-      <c r="C361" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="D361" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VN08</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>Maquinilla Orientador Varilla 25 mm</t>
-        </is>
-      </c>
-      <c r="C362" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="D362" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VN09</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>Escalerilla Cordón 25 mm</t>
-        </is>
-      </c>
-      <c r="C363" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D363" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VN10</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>Escalerilla Cinta 50 mm</t>
-        </is>
-      </c>
-      <c r="C364" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D364" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VN11</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>Soporte Techo / Pared 25 mm (Juego)</t>
-        </is>
-      </c>
-      <c r="C365" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D365" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VN12</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>Soporte Techo / Pared 50 mm (Juego)</t>
-        </is>
-      </c>
-      <c r="C366" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D366" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VN13</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>Motor Somfy para Veneciana 24V / 230V</t>
-        </is>
-      </c>
-      <c r="C367" t="n">
-        <v>145</v>
-      </c>
-      <c r="D367" t="n">
-        <v>108.75</v>
-      </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>FLX-VT-89</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>Cortina Vertical 89 mm - Colección Teide / Alcazaba</t>
-        </is>
-      </c>
-      <c r="C368" t="n">
-        <v>42</v>
-      </c>
-      <c r="D368" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>FLX-VT-127</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>Cortina Vertical 127 mm - Colección Teide / Alcazaba</t>
-        </is>
-      </c>
-      <c r="C369" t="n">
-        <v>38</v>
-      </c>
-      <c r="D369" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>FLX-VT-89M</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>Cortina Vertical 89 mm - Colección Mulhacén / Aneto</t>
-        </is>
-      </c>
-      <c r="C370" t="n">
-        <v>49</v>
-      </c>
-      <c r="D370" t="n">
-        <v>36.75</v>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>FLX-VT-127M</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>Cortina Vertical 127 mm - Colección Mulhacén / Aneto</t>
-        </is>
-      </c>
-      <c r="C371" t="n">
-        <v>44</v>
-      </c>
-      <c r="D371" t="n">
-        <v>33</v>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>FLX-VT-MAD</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>Cortina Vertical Madera 89 mm</t>
-        </is>
-      </c>
-      <c r="C372" t="n">
-        <v>111.8</v>
-      </c>
-      <c r="D372" t="n">
-        <v>83.84999999999999</v>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>FLX-VT-CUE</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>Cortina Vertical Cuero 89 mm</t>
-        </is>
-      </c>
-      <c r="C373" t="n">
-        <v>141.85</v>
-      </c>
-      <c r="D373" t="n">
-        <v>106.39</v>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VT01</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>Riel Vertical Aluminio Blanco / Plata</t>
-        </is>
-      </c>
-      <c r="C374" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="D374" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G374" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VT02</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>Carro Arrastre Vertical con Gancho</t>
-        </is>
-      </c>
-      <c r="C375" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="D375" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VT03</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>Cadena de Distancia Inferior 89 mm</t>
-        </is>
-      </c>
-      <c r="C376" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D376" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G376" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VT04</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>Cadena de Distancia Inferior 127 mm</t>
-        </is>
-      </c>
-      <c r="C377" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="D377" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VT05</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>Contrapeso Inferior 89 mm</t>
-        </is>
-      </c>
-      <c r="C378" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="D378" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VT06</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>Contrapeso Inferior 127 mm</t>
-        </is>
-      </c>
-      <c r="C379" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D379" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>FLX-CMP-VT07</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>Motor para Cortina Vertical 230V con Mando</t>
-        </is>
-      </c>
-      <c r="C380" t="n">
-        <v>365</v>
-      </c>
-      <c r="D380" t="n">
-        <v>273.75</v>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>FLX-PLI-01</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>Cortina Plisada Premium PLI.01 - Colección 236</t>
-        </is>
-      </c>
-      <c r="C381" t="n">
-        <v>58</v>
-      </c>
-      <c r="D381" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G381" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>FLX-PLI-REV</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>Cortina Plisada Repliegue Reversible PLI.02</t>
-        </is>
-      </c>
-      <c r="C382" t="n">
-        <v>68</v>
-      </c>
-      <c r="D382" t="n">
-        <v>51</v>
-      </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>FLX-PLI-ND</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>Cortina Plisada Noche y Día PLI.03</t>
-        </is>
-      </c>
-      <c r="C383" t="n">
-        <v>85</v>
-      </c>
-      <c r="D383" t="n">
-        <v>63.75</v>
-      </c>
-      <c r="E383" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>FLX-PLI-PLI</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>Cortina Plisada Plano Inclinado / Buhardilla PLI.04</t>
-        </is>
-      </c>
-      <c r="C384" t="n">
-        <v>74</v>
-      </c>
-      <c r="D384" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>FLX-PLI-MONO</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>Cortina Plisada Plus Monocomando PLI.05</t>
-        </is>
-      </c>
-      <c r="C385" t="n">
-        <v>79</v>
-      </c>
-      <c r="D385" t="n">
-        <v>59.25</v>
-      </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>FLX-PLI-MINI</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>Cortina Plisada Mini Cristal Accionamiento Manual</t>
-        </is>
-      </c>
-      <c r="C386" t="n">
-        <v>49</v>
-      </c>
-      <c r="D386" t="n">
-        <v>36.75</v>
-      </c>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>FLX-PLI-MINIC</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>Cortina Plisada Mini Accionamiento Cordón</t>
-        </is>
-      </c>
-      <c r="C387" t="n">
-        <v>45</v>
-      </c>
-      <c r="D387" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G387" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>FLX-CMP-PL01</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>Perfil Plisada Mini Cristal Blanco (13,3 x 20 mm)</t>
-        </is>
-      </c>
-      <c r="C388" t="n">
-        <v>19.15</v>
-      </c>
-      <c r="D388" t="n">
-        <v>14.36</v>
-      </c>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>FLX-CMP-PL02</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>Perfil Fijo Mini Cristal</t>
-        </is>
-      </c>
-      <c r="C389" t="n">
-        <v>15.81</v>
-      </c>
-      <c r="D389" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>FLX-CMP-PL03</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>Soporte Tensor Mini Modelo B</t>
-        </is>
-      </c>
-      <c r="C390" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D390" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>FLX-CMP-PL04</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>Freno Cordón Plisada Mini</t>
-        </is>
-      </c>
-      <c r="C391" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D391" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>FLX-CMP-PL05</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>Cordoncillo Plisada 1,2 mm</t>
-        </is>
-      </c>
-      <c r="C392" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="D392" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E392" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F392" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>FLX-PLE-01</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>Cortina Plegable Confeccionada Sistema Plus PLE.01</t>
-        </is>
-      </c>
-      <c r="C393" t="n">
-        <v>55</v>
-      </c>
-      <c r="D393" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="E393" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>FLX-PLE-LON</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>Cortina Plegable La Loneta PLE.05</t>
-        </is>
-      </c>
-      <c r="C394" t="n">
-        <v>62</v>
-      </c>
-      <c r="D394" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>FLX-PLE-VIS</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>Cortina Plegable El Visillo PLE.06</t>
-        </is>
-      </c>
-      <c r="C395" t="n">
-        <v>58</v>
-      </c>
-      <c r="D395" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>FLX-CMP-PLE01</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>Mecanismo Plegable a Cadena con Reductor</t>
-        </is>
-      </c>
-      <c r="C396" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="D396" t="n">
-        <v>16.88</v>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>FLX-CMP-PLE02</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>Perfil Velcrado Plegable Plus</t>
-        </is>
-      </c>
-      <c r="C397" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="D397" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>FLX-CMP-PLE03</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>Pletina Inferior Aluminio Plegable 40 mm</t>
-        </is>
-      </c>
-      <c r="C398" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="D398" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E398" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>FLX-CMP-PLE04</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>Varilla Fibra de Vidrio Plegable 4 mm</t>
-        </is>
-      </c>
-      <c r="C399" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D399" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>FLX-PAN-2V</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>Panel Deslizante / Japonés 2 Vías Sistema Básico</t>
-        </is>
-      </c>
-      <c r="C400" t="n">
-        <v>48</v>
-      </c>
-      <c r="D400" t="n">
-        <v>36</v>
-      </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>FLX-PAN-3V</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>Panel Deslizante / Japonés 3 Vías Sistema Básico</t>
-        </is>
-      </c>
-      <c r="C401" t="n">
-        <v>65</v>
-      </c>
-      <c r="D401" t="n">
-        <v>48.75</v>
-      </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>FLX-PAN-4V</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>Panel Deslizante / Japonés 4 Vías Sistema Básico</t>
-        </is>
-      </c>
-      <c r="C402" t="n">
-        <v>82</v>
-      </c>
-      <c r="D402" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>FLX-PAN-5V</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Panel Deslizante / Japonés 5 Vías Sistema Básico</t>
-        </is>
-      </c>
-      <c r="C403" t="n">
-        <v>98</v>
-      </c>
-      <c r="D403" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F403" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>FLX-PAN-MOT</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>Panel Deslizante Sistema Motor 3 a 5 Vías</t>
-        </is>
-      </c>
-      <c r="C404" t="n">
-        <v>280</v>
-      </c>
-      <c r="D404" t="n">
-        <v>210</v>
-      </c>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>FLX-CMP-PAN01</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>Portatela Velcrado Deslizante</t>
-        </is>
-      </c>
-      <c r="C405" t="n">
-        <v>19.77</v>
-      </c>
-      <c r="D405" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>FLX-CMP-PAN02</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>Trineo Arrastre Panel Deslizante</t>
-        </is>
-      </c>
-      <c r="C406" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="D406" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>FLX-CMP-PAN03</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Varilla de Mando Tirador 1,50 m</t>
-        </is>
-      </c>
-      <c r="C407" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="D407" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>FLX-ENR-UNI</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>Cortina Enrollable Universal EN.0 (Sin Tejido)</t>
-        </is>
-      </c>
-      <c r="C408" t="n">
-        <v>28</v>
-      </c>
-      <c r="D408" t="n">
-        <v>21</v>
-      </c>
-      <c r="E408" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F408" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G408" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>FLX-ENR-SAT</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>Cortina Enrollable Screen Satiné 5500</t>
-        </is>
-      </c>
-      <c r="C409" t="n">
-        <v>63</v>
-      </c>
-      <c r="D409" t="n">
-        <v>47.25</v>
-      </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F409" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>FLX-ENR-KAR</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Cortina Enrollable Screen Karellis 11301</t>
-        </is>
-      </c>
-      <c r="C410" t="n">
-        <v>68</v>
-      </c>
-      <c r="D410" t="n">
-        <v>51</v>
-      </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>FLX-ENR-OPA</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>Cortina Enrollable Tejido Opaco Vela</t>
-        </is>
-      </c>
-      <c r="C411" t="n">
-        <v>54</v>
-      </c>
-      <c r="D411" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>FLX-ENR-BAL</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>Cortina Enrollable Tejido Bali / Madeira EN.06</t>
-        </is>
-      </c>
-      <c r="C412" t="n">
-        <v>72</v>
-      </c>
-      <c r="D412" t="n">
-        <v>54</v>
-      </c>
-      <c r="E412" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>FLX-ENR-CAJ42</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>Cortina Enrollable con Cajón de 42 mm</t>
-        </is>
-      </c>
-      <c r="C413" t="n">
-        <v>72</v>
-      </c>
-      <c r="D413" t="n">
-        <v>54</v>
-      </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>FLX-ENR-CAJ90</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>Cortina Enrollable con Cajón de 90 mm CA.04</t>
-        </is>
-      </c>
-      <c r="C414" t="n">
-        <v>98</v>
-      </c>
-      <c r="D414" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>FLX-ENR-ZIP</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>Cortina Enrollable Sistema ZIP Guiada</t>
-        </is>
-      </c>
-      <c r="C415" t="n">
-        <v>135</v>
-      </c>
-      <c r="D415" t="n">
-        <v>101.25</v>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>FLX-ENR-CAB</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>Cortina Enrollable Guiada a Cable de Acero</t>
-        </is>
-      </c>
-      <c r="C416" t="n">
-        <v>78</v>
-      </c>
-      <c r="D416" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>FLX-ENR-BUH</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Cortina Enrollable Buhardilla con Guías Laterales</t>
-        </is>
-      </c>
-      <c r="C417" t="n">
-        <v>85</v>
-      </c>
-      <c r="D417" t="n">
-        <v>63.75</v>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>FLX-LM-01</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Cortina Luz Mágica LM.01 Alborada Galería 80</t>
-        </is>
-      </c>
-      <c r="C418" t="n">
-        <v>88</v>
-      </c>
-      <c r="D418" t="n">
-        <v>66</v>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>FLX-LM-03</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Cortina Luz Mágica LM.03 Niebla Galería 90</t>
-        </is>
-      </c>
-      <c r="C419" t="n">
-        <v>96</v>
-      </c>
-      <c r="D419" t="n">
-        <v>72</v>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN01</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Eje Aluminio D.43 mm para Enrollable</t>
-        </is>
-      </c>
-      <c r="C420" t="n">
-        <v>9.76</v>
-      </c>
-      <c r="D420" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN02</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Eje Aluminio D.58 mm para Enrollable</t>
-        </is>
-      </c>
-      <c r="C421" t="n">
-        <v>19.92</v>
-      </c>
-      <c r="D421" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN03</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Eje Aluminio D.80 mm para Enrollable</t>
-        </is>
-      </c>
-      <c r="C422" t="n">
-        <v>34.52</v>
-      </c>
-      <c r="D422" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN04</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Mecanismo Cadena D.43 Desmultiplicado 1:3</t>
-        </is>
-      </c>
-      <c r="C423" t="n">
-        <v>19.06</v>
-      </c>
-      <c r="D423" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN05</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Mecanismo Cadena D.58 Desmultiplicado 1:4</t>
-        </is>
-      </c>
-      <c r="C424" t="n">
-        <v>39.26</v>
-      </c>
-      <c r="D424" t="n">
-        <v>29.45</v>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN06</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Cadena Mando PVC 4,5 x 6 mm Cerrada 1,50 m</t>
-        </is>
-      </c>
-      <c r="C425" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="D425" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN07</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Cadena Mando PVC 4,5 x 6 mm Cerrada 2,00 m</t>
-        </is>
-      </c>
-      <c r="C426" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="D426" t="n">
-        <v>4</v>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN08</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Cadena Mando Metálica Continua</t>
-        </is>
-      </c>
-      <c r="C427" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D427" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN09</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Soportes Pared / Techo Enrollable 40 mm (Juego)</t>
-        </is>
-      </c>
-      <c r="C428" t="n">
-        <v>5</v>
-      </c>
-      <c r="D428" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN10</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Soportes Pared / Techo Enrollable 60 mm (Juego)</t>
-        </is>
-      </c>
-      <c r="C429" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="D429" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN11</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>Soportes Pared / Techo Enrollable 75 mm (Juego)</t>
-        </is>
-      </c>
-      <c r="C430" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="D430" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN12</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>Cajón de Aluminio 90 mm Curvo / Recto</t>
-        </is>
-      </c>
-      <c r="C431" t="n">
-        <v>33.51</v>
-      </c>
-      <c r="D431" t="n">
-        <v>25.13</v>
-      </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN13</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>Guía ZIP 50 x 34 mm con Clip</t>
-        </is>
-      </c>
-      <c r="C432" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="D432" t="n">
-        <v>16.95</v>
-      </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN14</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>Guía Ventilada Blanca con Pistón</t>
-        </is>
-      </c>
-      <c r="C433" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="D433" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN15</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>Guía Cerrada 55 mm Instalación en Hueco / Frontal</t>
-        </is>
-      </c>
-      <c r="C434" t="n">
-        <v>19.92</v>
-      </c>
-      <c r="D434" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>ml.</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN16</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>Accionamiento a Manivela Máquina 1:8 con Manivela 1,50 m</t>
-        </is>
-      </c>
-      <c r="C435" t="n">
-        <v>205</v>
-      </c>
-      <c r="D435" t="n">
-        <v>153.75</v>
-      </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>FLX-CMP-EN17</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>Motorización Somfy para Enrollable D.40 / D.50</t>
-        </is>
-      </c>
-      <c r="C436" t="n">
-        <v>165</v>
-      </c>
-      <c r="D436" t="n">
-        <v>123.75</v>
-      </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>ud.</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>Flexol</t>
-        </is>
-      </c>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>extracted_images/motor_p1_600500001.png</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/precios_catalogo.xlsx
+++ b/precios_catalogo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G265"/>
+  <dimension ref="A1:G275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9073,6 +9073,296 @@
       </c>
       <c r="G265" t="inlineStr"/>
     </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>FLX-5201</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>SCREENFLEX (Poliéster) - PL. 5201</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>65</v>
+      </c>
+      <c r="D266" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>FLX-4153</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>SCREENFLEX (Poliéster) - PL. 4153</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>62</v>
+      </c>
+      <c r="D267" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>FLX-4155</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>SCREENFLEX (Poliéster) - PL. 4155 (Colores especiales +10%)</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>59</v>
+      </c>
+      <c r="D268" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>FLX-LISBOA</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>LISBOA Opaco</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>69</v>
+      </c>
+      <c r="D269" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>FLX-SHANTUNG</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>SHANTUNG</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>48</v>
+      </c>
+      <c r="D270" t="n">
+        <v>36</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>FLX-4241</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>SCREENFLEX (Fibra de Vidrio) - FV. 4241</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>71</v>
+      </c>
+      <c r="D271" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>FLX-3903</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>SCREENFLEX (Fibra de Vidrio) - FV. 3903</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>68</v>
+      </c>
+      <c r="D272" t="n">
+        <v>51</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>FLX-3935</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>SCREENFLEX (Fibra de Vidrio) - FV. 3935</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>65</v>
+      </c>
+      <c r="D273" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>FLX-MALITR</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>MALI Traslúcido</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>48</v>
+      </c>
+      <c r="D274" t="n">
+        <v>36</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>FLX-MALIOP</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>MALI Opaco</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>60</v>
+      </c>
+      <c r="D275" t="n">
+        <v>45</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Flexol</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/precios_catalogo.xlsx
+++ b/precios_catalogo.xlsx
@@ -9139,7 +9139,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>SCREENFLEX (Poliéster) - PL. 4155 (Colores especiales +10%)</t>
+          <t>SCREENFLEX (Poliéster) - PL. 4155</t>
         </is>
       </c>
       <c r="C268" t="n">
